--- a/report.xlsx
+++ b/report.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I470"/>
+  <dimension ref="A1:I471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15006,6 +15006,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="471"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/report.xlsx
+++ b/report.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I471"/>
+  <dimension ref="A1:I486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15006,7 +15006,502 @@
         <v>0</v>
       </c>
     </row>
-    <row r="471"/>
+    <row r="471">
+      <c r="A471" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B471" s="2" t="n">
+        <v>0.3645833333333333</v>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Camera_2026-09-09_08-45-00.mp4</t>
+        </is>
+      </c>
+      <c r="D471" t="n">
+        <v>900</v>
+      </c>
+      <c r="E471" t="n">
+        <v>1</v>
+      </c>
+      <c r="F471" t="n">
+        <v>1</v>
+      </c>
+      <c r="G471" t="n">
+        <v>2</v>
+      </c>
+      <c r="H471" t="n">
+        <v>898</v>
+      </c>
+      <c r="I471" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B472" s="2" t="n">
+        <v>0.3750347222222222</v>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Camera_2026-09-09_09-00-03.mp4</t>
+        </is>
+      </c>
+      <c r="D472" t="n">
+        <v>900</v>
+      </c>
+      <c r="E472" t="n">
+        <v>0</v>
+      </c>
+      <c r="F472" t="n">
+        <v>1</v>
+      </c>
+      <c r="G472" t="n">
+        <v>0</v>
+      </c>
+      <c r="H472" t="n">
+        <v>900</v>
+      </c>
+      <c r="I472" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B473" s="2" t="n">
+        <v>0.3854513888888889</v>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Camera_2026-09-09_09-15-03.mp4</t>
+        </is>
+      </c>
+      <c r="D473" t="n">
+        <v>900</v>
+      </c>
+      <c r="E473" t="n">
+        <v>0</v>
+      </c>
+      <c r="F473" t="n">
+        <v>1</v>
+      </c>
+      <c r="G473" t="n">
+        <v>0</v>
+      </c>
+      <c r="H473" t="n">
+        <v>900</v>
+      </c>
+      <c r="I473" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B474" s="2" t="n">
+        <v>0.3958680555555555</v>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Camera_2026-09-09_09-30-03.mp4</t>
+        </is>
+      </c>
+      <c r="D474" t="n">
+        <v>900</v>
+      </c>
+      <c r="E474" t="n">
+        <v>0</v>
+      </c>
+      <c r="F474" t="n">
+        <v>1</v>
+      </c>
+      <c r="G474" t="n">
+        <v>0</v>
+      </c>
+      <c r="H474" t="n">
+        <v>900</v>
+      </c>
+      <c r="I474" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B475" s="2" t="n">
+        <v>0.4062847222222222</v>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Camera_2026-09-09_09-45-03.mp4</t>
+        </is>
+      </c>
+      <c r="D475" t="n">
+        <v>900</v>
+      </c>
+      <c r="E475" t="n">
+        <v>0</v>
+      </c>
+      <c r="F475" t="n">
+        <v>1</v>
+      </c>
+      <c r="G475" t="n">
+        <v>0</v>
+      </c>
+      <c r="H475" t="n">
+        <v>900</v>
+      </c>
+      <c r="I475" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B476" s="2" t="n">
+        <v>0.4166898148148148</v>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Camera_2026-09-09_10-00-02.mp4</t>
+        </is>
+      </c>
+      <c r="D476" t="n">
+        <v>900</v>
+      </c>
+      <c r="E476" t="n">
+        <v>0</v>
+      </c>
+      <c r="F476" t="n">
+        <v>1</v>
+      </c>
+      <c r="G476" t="n">
+        <v>0</v>
+      </c>
+      <c r="H476" t="n">
+        <v>900</v>
+      </c>
+      <c r="I476" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B477" s="2" t="n">
+        <v>0.4271180555555555</v>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Camera_2026-09-09_10-15-03.mp4</t>
+        </is>
+      </c>
+      <c r="D477" t="n">
+        <v>900</v>
+      </c>
+      <c r="E477" t="n">
+        <v>0</v>
+      </c>
+      <c r="F477" t="n">
+        <v>1</v>
+      </c>
+      <c r="G477" t="n">
+        <v>0</v>
+      </c>
+      <c r="H477" t="n">
+        <v>900</v>
+      </c>
+      <c r="I477" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B478" s="2" t="n">
+        <v>0.4375347222222222</v>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Camera_2026-09-09_10-30-03.mp4</t>
+        </is>
+      </c>
+      <c r="D478" t="n">
+        <v>900</v>
+      </c>
+      <c r="E478" t="n">
+        <v>0</v>
+      </c>
+      <c r="F478" t="n">
+        <v>1</v>
+      </c>
+      <c r="G478" t="n">
+        <v>0</v>
+      </c>
+      <c r="H478" t="n">
+        <v>900</v>
+      </c>
+      <c r="I478" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B479" s="2" t="n">
+        <v>0.4479513888888889</v>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Camera_2026-09-09_10-45-03.mp4</t>
+        </is>
+      </c>
+      <c r="D479" t="n">
+        <v>900</v>
+      </c>
+      <c r="E479" t="n">
+        <v>0</v>
+      </c>
+      <c r="F479" t="n">
+        <v>1</v>
+      </c>
+      <c r="G479" t="n">
+        <v>0</v>
+      </c>
+      <c r="H479" t="n">
+        <v>900</v>
+      </c>
+      <c r="I479" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B480" s="2" t="n">
+        <v>0.4583680555555555</v>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Camera_2026-09-09_11-00-03.mp4</t>
+        </is>
+      </c>
+      <c r="D480" t="n">
+        <v>900</v>
+      </c>
+      <c r="E480" t="n">
+        <v>0</v>
+      </c>
+      <c r="F480" t="n">
+        <v>1</v>
+      </c>
+      <c r="G480" t="n">
+        <v>0</v>
+      </c>
+      <c r="H480" t="n">
+        <v>900</v>
+      </c>
+      <c r="I480" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B481" s="2" t="n">
+        <v>0.4687847222222222</v>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Camera_2026-09-09_11-15-03.mp4</t>
+        </is>
+      </c>
+      <c r="D481" t="n">
+        <v>900</v>
+      </c>
+      <c r="E481" t="n">
+        <v>0</v>
+      </c>
+      <c r="F481" t="n">
+        <v>1</v>
+      </c>
+      <c r="G481" t="n">
+        <v>0</v>
+      </c>
+      <c r="H481" t="n">
+        <v>900</v>
+      </c>
+      <c r="I481" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B482" s="2" t="n">
+        <v>0.4792013888888889</v>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Camera_2026-09-09_11-30-03.mp4</t>
+        </is>
+      </c>
+      <c r="D482" t="n">
+        <v>900</v>
+      </c>
+      <c r="E482" t="n">
+        <v>0</v>
+      </c>
+      <c r="F482" t="n">
+        <v>1</v>
+      </c>
+      <c r="G482" t="n">
+        <v>0</v>
+      </c>
+      <c r="H482" t="n">
+        <v>900</v>
+      </c>
+      <c r="I482" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B483" s="2" t="n">
+        <v>0.3958333333333333</v>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Camera_2026-09-09_09-30-00_combined.mp4</t>
+        </is>
+      </c>
+      <c r="D483" t="n">
+        <v>96.56699999999999</v>
+      </c>
+      <c r="E483" t="n">
+        <v>49</v>
+      </c>
+      <c r="F483" t="n">
+        <v>0</v>
+      </c>
+      <c r="G483" t="n">
+        <v>96.56699999999999</v>
+      </c>
+      <c r="H483" t="n">
+        <v>0</v>
+      </c>
+      <c r="I483" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B484" s="2" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Camera_2026-09-09_10-00-00_combined.mp4</t>
+        </is>
+      </c>
+      <c r="D484" t="n">
+        <v>403.7</v>
+      </c>
+      <c r="E484" t="n">
+        <v>209</v>
+      </c>
+      <c r="F484" t="n">
+        <v>0</v>
+      </c>
+      <c r="G484" t="n">
+        <v>403.7</v>
+      </c>
+      <c r="H484" t="n">
+        <v>0</v>
+      </c>
+      <c r="I484" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B485" s="2" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Camera_2026-09-09_10-30-00_combined.mp4</t>
+        </is>
+      </c>
+      <c r="D485" t="n">
+        <v>404.167</v>
+      </c>
+      <c r="E485" t="n">
+        <v>209</v>
+      </c>
+      <c r="F485" t="n">
+        <v>0</v>
+      </c>
+      <c r="G485" t="n">
+        <v>404.167</v>
+      </c>
+      <c r="H485" t="n">
+        <v>0</v>
+      </c>
+      <c r="I485" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="1" t="n">
+        <v>46274</v>
+      </c>
+      <c r="B486" s="2" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Camera_2026-09-09_11-00-00_combined.mp4</t>
+        </is>
+      </c>
+      <c r="D486" t="n">
+        <v>346.467</v>
+      </c>
+      <c r="E486" t="n">
+        <v>179</v>
+      </c>
+      <c r="F486" t="n">
+        <v>0</v>
+      </c>
+      <c r="G486" t="n">
+        <v>346.467</v>
+      </c>
+      <c r="H486" t="n">
+        <v>0</v>
+      </c>
+      <c r="I486" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/report.xlsx
+++ b/report.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I486"/>
+  <dimension ref="A1:J486"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
           <t>Corrupted_segments</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -497,6 +502,11 @@
       <c r="I2" t="n">
         <v>0</v>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -528,6 +538,11 @@
       <c r="I3" t="n">
         <v>0</v>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -559,6 +574,11 @@
       <c r="I4" t="n">
         <v>0</v>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
@@ -590,6 +610,11 @@
       <c r="I5" t="n">
         <v>0</v>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
@@ -621,6 +646,11 @@
       <c r="I6" t="n">
         <v>0</v>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
@@ -652,6 +682,11 @@
       <c r="I7" t="n">
         <v>0</v>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
@@ -683,6 +718,11 @@
       <c r="I8" t="n">
         <v>0</v>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
@@ -714,6 +754,11 @@
       <c r="I9" t="n">
         <v>0</v>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
@@ -745,6 +790,11 @@
       <c r="I10" t="n">
         <v>0</v>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -776,6 +826,11 @@
       <c r="I11" t="n">
         <v>0</v>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -807,6 +862,11 @@
       <c r="I12" t="n">
         <v>0</v>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
@@ -838,6 +898,11 @@
       <c r="I13" t="n">
         <v>0</v>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
@@ -869,6 +934,11 @@
       <c r="I14" t="n">
         <v>0</v>
       </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -900,6 +970,11 @@
       <c r="I15" t="n">
         <v>0</v>
       </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
@@ -931,6 +1006,11 @@
       <c r="I16" t="n">
         <v>0</v>
       </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
@@ -962,6 +1042,11 @@
       <c r="I17" t="n">
         <v>0</v>
       </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
@@ -993,6 +1078,11 @@
       <c r="I18" t="n">
         <v>0</v>
       </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1024,6 +1114,11 @@
       <c r="I19" t="n">
         <v>0</v>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
@@ -1055,6 +1150,11 @@
       <c r="I20" t="n">
         <v>0</v>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1086,6 +1186,11 @@
       <c r="I21" t="n">
         <v>0</v>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
@@ -1117,6 +1222,11 @@
       <c r="I22" t="n">
         <v>0</v>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
@@ -1148,6 +1258,11 @@
       <c r="I23" t="n">
         <v>0</v>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
@@ -1179,6 +1294,11 @@
       <c r="I24" t="n">
         <v>0</v>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
@@ -1210,6 +1330,11 @@
       <c r="I25" t="n">
         <v>0</v>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
@@ -1241,6 +1366,11 @@
       <c r="I26" t="n">
         <v>0</v>
       </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -1272,6 +1402,11 @@
       <c r="I27" t="n">
         <v>0</v>
       </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -1303,6 +1438,11 @@
       <c r="I28" t="n">
         <v>0</v>
       </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -1334,6 +1474,11 @@
       <c r="I29" t="n">
         <v>0</v>
       </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -1365,6 +1510,11 @@
       <c r="I30" t="n">
         <v>0</v>
       </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -1396,6 +1546,11 @@
       <c r="I31" t="n">
         <v>0</v>
       </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -1427,6 +1582,11 @@
       <c r="I32" t="n">
         <v>0</v>
       </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
@@ -1458,6 +1618,11 @@
       <c r="I33" t="n">
         <v>0</v>
       </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
@@ -1489,6 +1654,11 @@
       <c r="I34" t="n">
         <v>0</v>
       </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
@@ -1520,6 +1690,11 @@
       <c r="I35" t="n">
         <v>0</v>
       </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
@@ -1551,6 +1726,11 @@
       <c r="I36" t="n">
         <v>0</v>
       </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
@@ -1582,6 +1762,11 @@
       <c r="I37" t="n">
         <v>0</v>
       </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
@@ -1613,6 +1798,11 @@
       <c r="I38" t="n">
         <v>0</v>
       </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
@@ -1644,6 +1834,11 @@
       <c r="I39" t="n">
         <v>0</v>
       </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
@@ -1675,6 +1870,11 @@
       <c r="I40" t="n">
         <v>0</v>
       </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
@@ -1706,6 +1906,11 @@
       <c r="I41" t="n">
         <v>0</v>
       </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
@@ -1737,6 +1942,11 @@
       <c r="I42" t="n">
         <v>0</v>
       </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
@@ -1768,6 +1978,11 @@
       <c r="I43" t="n">
         <v>0</v>
       </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
@@ -1799,6 +2014,11 @@
       <c r="I44" t="n">
         <v>0</v>
       </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -1830,6 +2050,11 @@
       <c r="I45" t="n">
         <v>0</v>
       </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -1861,6 +2086,11 @@
       <c r="I46" t="n">
         <v>0</v>
       </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
@@ -1892,6 +2122,11 @@
       <c r="I47" t="n">
         <v>0</v>
       </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
@@ -1923,6 +2158,11 @@
       <c r="I48" t="n">
         <v>0</v>
       </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -1954,6 +2194,11 @@
       <c r="I49" t="n">
         <v>0</v>
       </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -1985,6 +2230,11 @@
       <c r="I50" t="n">
         <v>0</v>
       </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
@@ -2016,6 +2266,11 @@
       <c r="I51" t="n">
         <v>0</v>
       </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
@@ -2047,6 +2302,11 @@
       <c r="I52" t="n">
         <v>0</v>
       </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
@@ -2078,6 +2338,11 @@
       <c r="I53" t="n">
         <v>0</v>
       </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -2109,6 +2374,11 @@
       <c r="I54" t="n">
         <v>0</v>
       </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -2140,6 +2410,11 @@
       <c r="I55" t="n">
         <v>0</v>
       </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -2171,6 +2446,11 @@
       <c r="I56" t="n">
         <v>0</v>
       </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -2202,6 +2482,11 @@
       <c r="I57" t="n">
         <v>0</v>
       </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -2233,6 +2518,11 @@
       <c r="I58" t="n">
         <v>0</v>
       </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -2264,6 +2554,11 @@
       <c r="I59" t="n">
         <v>0</v>
       </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -2295,6 +2590,11 @@
       <c r="I60" t="n">
         <v>0</v>
       </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -2326,6 +2626,11 @@
       <c r="I61" t="n">
         <v>0</v>
       </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
@@ -2357,6 +2662,11 @@
       <c r="I62" t="n">
         <v>0</v>
       </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -2388,6 +2698,11 @@
       <c r="I63" t="n">
         <v>0</v>
       </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
@@ -2419,6 +2734,11 @@
       <c r="I64" t="n">
         <v>0</v>
       </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -2450,6 +2770,11 @@
       <c r="I65" t="n">
         <v>0</v>
       </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -2481,6 +2806,11 @@
       <c r="I66" t="n">
         <v>0</v>
       </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -2512,6 +2842,11 @@
       <c r="I67" t="n">
         <v>0</v>
       </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -2543,6 +2878,11 @@
       <c r="I68" t="n">
         <v>0</v>
       </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -2574,6 +2914,11 @@
       <c r="I69" t="n">
         <v>0</v>
       </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
@@ -2605,6 +2950,11 @@
       <c r="I70" t="n">
         <v>0</v>
       </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
@@ -2636,6 +2986,11 @@
       <c r="I71" t="n">
         <v>0</v>
       </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
@@ -2667,6 +3022,11 @@
       <c r="I72" t="n">
         <v>0</v>
       </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
@@ -2698,6 +3058,11 @@
       <c r="I73" t="n">
         <v>0</v>
       </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
@@ -2729,6 +3094,11 @@
       <c r="I74" t="n">
         <v>0</v>
       </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -2760,6 +3130,11 @@
       <c r="I75" t="n">
         <v>0</v>
       </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -2791,6 +3166,11 @@
       <c r="I76" t="n">
         <v>0</v>
       </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
@@ -2822,6 +3202,11 @@
       <c r="I77" t="n">
         <v>0</v>
       </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
@@ -2853,6 +3238,11 @@
       <c r="I78" t="n">
         <v>0</v>
       </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
@@ -2884,6 +3274,11 @@
       <c r="I79" t="n">
         <v>0</v>
       </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
@@ -2915,6 +3310,11 @@
       <c r="I80" t="n">
         <v>0</v>
       </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -2946,6 +3346,11 @@
       <c r="I81" t="n">
         <v>0</v>
       </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -2977,6 +3382,11 @@
       <c r="I82" t="n">
         <v>0</v>
       </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
@@ -3008,6 +3418,11 @@
       <c r="I83" t="n">
         <v>0</v>
       </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
@@ -3039,6 +3454,11 @@
       <c r="I84" t="n">
         <v>0</v>
       </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
@@ -3070,6 +3490,11 @@
       <c r="I85" t="n">
         <v>0</v>
       </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
@@ -3101,6 +3526,11 @@
       <c r="I86" t="n">
         <v>0</v>
       </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
@@ -3132,6 +3562,11 @@
       <c r="I87" t="n">
         <v>0</v>
       </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -3163,6 +3598,11 @@
       <c r="I88" t="n">
         <v>0</v>
       </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
@@ -3194,6 +3634,11 @@
       <c r="I89" t="n">
         <v>0</v>
       </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
@@ -3225,6 +3670,11 @@
       <c r="I90" t="n">
         <v>0</v>
       </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
@@ -3256,6 +3706,11 @@
       <c r="I91" t="n">
         <v>0</v>
       </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
@@ -3287,6 +3742,11 @@
       <c r="I92" t="n">
         <v>0</v>
       </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
@@ -3318,6 +3778,11 @@
       <c r="I93" t="n">
         <v>0</v>
       </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
@@ -3349,6 +3814,11 @@
       <c r="I94" t="n">
         <v>0</v>
       </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
@@ -3380,6 +3850,11 @@
       <c r="I95" t="n">
         <v>0</v>
       </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -3411,6 +3886,11 @@
       <c r="I96" t="n">
         <v>0</v>
       </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -3442,6 +3922,11 @@
       <c r="I97" t="n">
         <v>0</v>
       </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
@@ -3473,6 +3958,11 @@
       <c r="I98" t="n">
         <v>0</v>
       </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
@@ -3504,6 +3994,11 @@
       <c r="I99" t="n">
         <v>0</v>
       </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
@@ -3535,6 +4030,11 @@
       <c r="I100" t="n">
         <v>0</v>
       </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
@@ -3566,6 +4066,11 @@
       <c r="I101" t="n">
         <v>0</v>
       </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -3597,6 +4102,11 @@
       <c r="I102" t="n">
         <v>0</v>
       </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -3628,6 +4138,11 @@
       <c r="I103" t="n">
         <v>0</v>
       </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
@@ -3659,6 +4174,11 @@
       <c r="I104" t="n">
         <v>0</v>
       </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
@@ -3690,6 +4210,11 @@
       <c r="I105" t="n">
         <v>0</v>
       </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
@@ -3721,6 +4246,11 @@
       <c r="I106" t="n">
         <v>0</v>
       </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -3752,6 +4282,11 @@
       <c r="I107" t="n">
         <v>0</v>
       </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -3783,6 +4318,11 @@
       <c r="I108" t="n">
         <v>0</v>
       </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
@@ -3814,6 +4354,11 @@
       <c r="I109" t="n">
         <v>0</v>
       </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
@@ -3845,6 +4390,11 @@
       <c r="I110" t="n">
         <v>0</v>
       </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
@@ -3876,6 +4426,11 @@
       <c r="I111" t="n">
         <v>0</v>
       </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
@@ -3907,6 +4462,11 @@
       <c r="I112" t="n">
         <v>0</v>
       </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -3938,6 +4498,11 @@
       <c r="I113" t="n">
         <v>0</v>
       </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -3969,6 +4534,11 @@
       <c r="I114" t="n">
         <v>0</v>
       </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
@@ -4000,6 +4570,11 @@
       <c r="I115" t="n">
         <v>0</v>
       </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
@@ -4031,6 +4606,11 @@
       <c r="I116" t="n">
         <v>0</v>
       </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -4062,6 +4642,11 @@
       <c r="I117" t="n">
         <v>0</v>
       </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -4093,6 +4678,11 @@
       <c r="I118" t="n">
         <v>0</v>
       </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -4124,6 +4714,11 @@
       <c r="I119" t="n">
         <v>0</v>
       </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -4155,6 +4750,11 @@
       <c r="I120" t="n">
         <v>0</v>
       </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -4186,6 +4786,11 @@
       <c r="I121" t="n">
         <v>0</v>
       </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -4217,6 +4822,11 @@
       <c r="I122" t="n">
         <v>0</v>
       </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -4248,6 +4858,11 @@
       <c r="I123" t="n">
         <v>0</v>
       </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -4279,6 +4894,11 @@
       <c r="I124" t="n">
         <v>0</v>
       </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -4310,6 +4930,11 @@
       <c r="I125" t="n">
         <v>0</v>
       </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -4341,6 +4966,11 @@
       <c r="I126" t="n">
         <v>0</v>
       </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -4372,6 +5002,11 @@
       <c r="I127" t="n">
         <v>0</v>
       </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -4403,6 +5038,11 @@
       <c r="I128" t="n">
         <v>0</v>
       </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
@@ -4434,6 +5074,11 @@
       <c r="I129" t="n">
         <v>0</v>
       </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
@@ -4465,6 +5110,11 @@
       <c r="I130" t="n">
         <v>0</v>
       </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
@@ -4496,6 +5146,11 @@
       <c r="I131" t="n">
         <v>0</v>
       </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
@@ -4527,6 +5182,11 @@
       <c r="I132" t="n">
         <v>0</v>
       </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
@@ -4558,6 +5218,11 @@
       <c r="I133" t="n">
         <v>0</v>
       </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
@@ -4589,6 +5254,11 @@
       <c r="I134" t="n">
         <v>0</v>
       </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
@@ -4620,6 +5290,11 @@
       <c r="I135" t="n">
         <v>0</v>
       </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
@@ -4651,6 +5326,11 @@
       <c r="I136" t="n">
         <v>0</v>
       </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
@@ -4682,6 +5362,11 @@
       <c r="I137" t="n">
         <v>0</v>
       </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
@@ -4713,6 +5398,11 @@
       <c r="I138" t="n">
         <v>0</v>
       </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -4744,6 +5434,11 @@
       <c r="I139" t="n">
         <v>0</v>
       </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -4775,6 +5470,11 @@
       <c r="I140" t="n">
         <v>0</v>
       </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
@@ -4806,6 +5506,11 @@
       <c r="I141" t="n">
         <v>0</v>
       </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
@@ -4837,6 +5542,11 @@
       <c r="I142" t="n">
         <v>0</v>
       </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
@@ -4868,6 +5578,11 @@
       <c r="I143" t="n">
         <v>0</v>
       </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
@@ -4899,6 +5614,11 @@
       <c r="I144" t="n">
         <v>0</v>
       </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
@@ -4930,6 +5650,11 @@
       <c r="I145" t="n">
         <v>0</v>
       </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
@@ -4961,6 +5686,11 @@
       <c r="I146" t="n">
         <v>0</v>
       </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
@@ -4992,6 +5722,11 @@
       <c r="I147" t="n">
         <v>0</v>
       </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -5023,6 +5758,11 @@
       <c r="I148" t="n">
         <v>0</v>
       </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -5054,6 +5794,11 @@
       <c r="I149" t="n">
         <v>0</v>
       </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
@@ -5085,6 +5830,11 @@
       <c r="I150" t="n">
         <v>0</v>
       </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
@@ -5116,6 +5866,11 @@
       <c r="I151" t="n">
         <v>0</v>
       </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -5147,6 +5902,11 @@
       <c r="I152" t="n">
         <v>0</v>
       </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -5178,6 +5938,11 @@
       <c r="I153" t="n">
         <v>0</v>
       </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
@@ -5209,6 +5974,11 @@
       <c r="I154" t="n">
         <v>0</v>
       </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -5240,6 +6010,11 @@
       <c r="I155" t="n">
         <v>0</v>
       </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -5271,6 +6046,11 @@
       <c r="I156" t="n">
         <v>0</v>
       </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -5302,6 +6082,11 @@
       <c r="I157" t="n">
         <v>0</v>
       </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
@@ -5333,6 +6118,11 @@
       <c r="I158" t="n">
         <v>0</v>
       </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
@@ -5364,6 +6154,11 @@
       <c r="I159" t="n">
         <v>0</v>
       </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -5395,6 +6190,11 @@
       <c r="I160" t="n">
         <v>0</v>
       </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -5426,6 +6226,11 @@
       <c r="I161" t="n">
         <v>0</v>
       </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
@@ -5457,6 +6262,11 @@
       <c r="I162" t="n">
         <v>0</v>
       </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
@@ -5488,6 +6298,11 @@
       <c r="I163" t="n">
         <v>0</v>
       </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -5519,6 +6334,11 @@
       <c r="I164" t="n">
         <v>0</v>
       </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -5550,6 +6370,11 @@
       <c r="I165" t="n">
         <v>0</v>
       </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
@@ -5581,6 +6406,11 @@
       <c r="I166" t="n">
         <v>0</v>
       </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
@@ -5612,6 +6442,11 @@
       <c r="I167" t="n">
         <v>0</v>
       </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -5643,6 +6478,11 @@
       <c r="I168" t="n">
         <v>0</v>
       </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -5674,6 +6514,11 @@
       <c r="I169" t="n">
         <v>0</v>
       </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
@@ -5705,6 +6550,11 @@
       <c r="I170" t="n">
         <v>0</v>
       </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
@@ -5736,6 +6586,11 @@
       <c r="I171" t="n">
         <v>0</v>
       </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
@@ -5767,6 +6622,11 @@
       <c r="I172" t="n">
         <v>0</v>
       </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
@@ -5798,6 +6658,11 @@
       <c r="I173" t="n">
         <v>0</v>
       </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
@@ -5829,6 +6694,11 @@
       <c r="I174" t="n">
         <v>0</v>
       </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
@@ -5860,6 +6730,11 @@
       <c r="I175" t="n">
         <v>0</v>
       </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
@@ -5891,6 +6766,11 @@
       <c r="I176" t="n">
         <v>0</v>
       </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
@@ -5922,6 +6802,11 @@
       <c r="I177" t="n">
         <v>0</v>
       </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
@@ -5953,6 +6838,11 @@
       <c r="I178" t="n">
         <v>0</v>
       </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
@@ -5984,6 +6874,11 @@
       <c r="I179" t="n">
         <v>0</v>
       </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
@@ -6015,6 +6910,11 @@
       <c r="I180" t="n">
         <v>0</v>
       </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
@@ -6046,6 +6946,11 @@
       <c r="I181" t="n">
         <v>0</v>
       </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
@@ -6077,6 +6982,11 @@
       <c r="I182" t="n">
         <v>0</v>
       </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
@@ -6108,6 +7018,11 @@
       <c r="I183" t="n">
         <v>0</v>
       </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
@@ -6139,6 +7054,11 @@
       <c r="I184" t="n">
         <v>0</v>
       </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
@@ -6170,6 +7090,11 @@
       <c r="I185" t="n">
         <v>0</v>
       </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
@@ -6201,6 +7126,11 @@
       <c r="I186" t="n">
         <v>0</v>
       </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
@@ -6232,6 +7162,11 @@
       <c r="I187" t="n">
         <v>0</v>
       </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
@@ -6263,6 +7198,11 @@
       <c r="I188" t="n">
         <v>0</v>
       </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
@@ -6294,6 +7234,11 @@
       <c r="I189" t="n">
         <v>0</v>
       </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
@@ -6325,6 +7270,11 @@
       <c r="I190" t="n">
         <v>0</v>
       </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
@@ -6356,6 +7306,11 @@
       <c r="I191" t="n">
         <v>0</v>
       </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
@@ -6387,6 +7342,11 @@
       <c r="I192" t="n">
         <v>0</v>
       </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
@@ -6418,6 +7378,11 @@
       <c r="I193" t="n">
         <v>0</v>
       </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
@@ -6449,6 +7414,11 @@
       <c r="I194" t="n">
         <v>0</v>
       </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
@@ -6480,6 +7450,11 @@
       <c r="I195" t="n">
         <v>0</v>
       </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
@@ -6511,6 +7486,11 @@
       <c r="I196" t="n">
         <v>0</v>
       </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
@@ -6542,6 +7522,11 @@
       <c r="I197" t="n">
         <v>0</v>
       </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
@@ -6573,6 +7558,11 @@
       <c r="I198" t="n">
         <v>0</v>
       </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
@@ -6604,6 +7594,11 @@
       <c r="I199" t="n">
         <v>0</v>
       </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
@@ -6635,6 +7630,11 @@
       <c r="I200" t="n">
         <v>0</v>
       </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
@@ -6666,6 +7666,11 @@
       <c r="I201" t="n">
         <v>0</v>
       </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
@@ -6697,6 +7702,11 @@
       <c r="I202" t="n">
         <v>0</v>
       </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
@@ -6728,6 +7738,11 @@
       <c r="I203" t="n">
         <v>0</v>
       </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
@@ -6759,6 +7774,11 @@
       <c r="I204" t="n">
         <v>0</v>
       </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
@@ -6790,6 +7810,11 @@
       <c r="I205" t="n">
         <v>0</v>
       </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
@@ -6821,6 +7846,11 @@
       <c r="I206" t="n">
         <v>0</v>
       </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
@@ -6852,6 +7882,11 @@
       <c r="I207" t="n">
         <v>0</v>
       </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
@@ -6883,6 +7918,11 @@
       <c r="I208" t="n">
         <v>0</v>
       </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
@@ -6914,6 +7954,11 @@
       <c r="I209" t="n">
         <v>0</v>
       </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
@@ -6945,6 +7990,11 @@
       <c r="I210" t="n">
         <v>0</v>
       </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
@@ -6976,6 +8026,11 @@
       <c r="I211" t="n">
         <v>0</v>
       </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
@@ -7007,6 +8062,11 @@
       <c r="I212" t="n">
         <v>0</v>
       </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
@@ -7038,6 +8098,11 @@
       <c r="I213" t="n">
         <v>0</v>
       </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
@@ -7069,6 +8134,11 @@
       <c r="I214" t="n">
         <v>0</v>
       </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
@@ -7100,6 +8170,11 @@
       <c r="I215" t="n">
         <v>0</v>
       </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
@@ -7131,6 +8206,11 @@
       <c r="I216" t="n">
         <v>0</v>
       </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
@@ -7162,6 +8242,11 @@
       <c r="I217" t="n">
         <v>0</v>
       </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
@@ -7193,6 +8278,11 @@
       <c r="I218" t="n">
         <v>0</v>
       </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
@@ -7224,6 +8314,11 @@
       <c r="I219" t="n">
         <v>0</v>
       </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
@@ -7255,6 +8350,11 @@
       <c r="I220" t="n">
         <v>0</v>
       </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
@@ -7286,6 +8386,11 @@
       <c r="I221" t="n">
         <v>0</v>
       </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
@@ -7317,6 +8422,11 @@
       <c r="I222" t="n">
         <v>0</v>
       </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
@@ -7348,6 +8458,11 @@
       <c r="I223" t="n">
         <v>0</v>
       </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
@@ -7379,6 +8494,11 @@
       <c r="I224" t="n">
         <v>0</v>
       </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
@@ -7410,6 +8530,11 @@
       <c r="I225" t="n">
         <v>0</v>
       </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
@@ -7441,6 +8566,11 @@
       <c r="I226" t="n">
         <v>0</v>
       </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
@@ -7472,6 +8602,11 @@
       <c r="I227" t="n">
         <v>0</v>
       </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
@@ -7503,6 +8638,11 @@
       <c r="I228" t="n">
         <v>0</v>
       </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
@@ -7534,6 +8674,11 @@
       <c r="I229" t="n">
         <v>0</v>
       </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
@@ -7565,6 +8710,11 @@
       <c r="I230" t="n">
         <v>0</v>
       </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
@@ -7596,6 +8746,11 @@
       <c r="I231" t="n">
         <v>0</v>
       </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
@@ -7627,6 +8782,11 @@
       <c r="I232" t="n">
         <v>0</v>
       </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
@@ -7658,6 +8818,11 @@
       <c r="I233" t="n">
         <v>0</v>
       </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
@@ -7689,6 +8854,11 @@
       <c r="I234" t="n">
         <v>0</v>
       </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
@@ -7720,6 +8890,11 @@
       <c r="I235" t="n">
         <v>0</v>
       </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
@@ -7751,6 +8926,11 @@
       <c r="I236" t="n">
         <v>0</v>
       </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
@@ -7782,6 +8962,11 @@
       <c r="I237" t="n">
         <v>0</v>
       </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
@@ -7813,6 +8998,11 @@
       <c r="I238" t="n">
         <v>0</v>
       </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
@@ -7844,6 +9034,11 @@
       <c r="I239" t="n">
         <v>0</v>
       </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
@@ -7875,6 +9070,11 @@
       <c r="I240" t="n">
         <v>0</v>
       </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
@@ -7906,6 +9106,11 @@
       <c r="I241" t="n">
         <v>0</v>
       </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
@@ -7937,6 +9142,11 @@
       <c r="I242" t="n">
         <v>0</v>
       </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
@@ -7968,6 +9178,11 @@
       <c r="I243" t="n">
         <v>0</v>
       </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
@@ -7999,6 +9214,11 @@
       <c r="I244" t="n">
         <v>0</v>
       </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
@@ -8030,6 +9250,11 @@
       <c r="I245" t="n">
         <v>0</v>
       </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
@@ -8061,6 +9286,11 @@
       <c r="I246" t="n">
         <v>0</v>
       </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
@@ -8092,6 +9322,11 @@
       <c r="I247" t="n">
         <v>0</v>
       </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
@@ -8123,6 +9358,11 @@
       <c r="I248" t="n">
         <v>0</v>
       </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
@@ -8154,6 +9394,11 @@
       <c r="I249" t="n">
         <v>0</v>
       </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
@@ -8185,6 +9430,11 @@
       <c r="I250" t="n">
         <v>0</v>
       </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
@@ -8216,6 +9466,11 @@
       <c r="I251" t="n">
         <v>0</v>
       </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
@@ -8247,6 +9502,11 @@
       <c r="I252" t="n">
         <v>0</v>
       </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
@@ -8278,6 +9538,11 @@
       <c r="I253" t="n">
         <v>0</v>
       </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="n">
@@ -8309,6 +9574,11 @@
       <c r="I254" t="n">
         <v>0</v>
       </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
@@ -8340,6 +9610,11 @@
       <c r="I255" t="n">
         <v>0</v>
       </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
@@ -8371,6 +9646,11 @@
       <c r="I256" t="n">
         <v>0</v>
       </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
@@ -8402,6 +9682,11 @@
       <c r="I257" t="n">
         <v>0</v>
       </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
@@ -8433,6 +9718,11 @@
       <c r="I258" t="n">
         <v>0</v>
       </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
@@ -8464,6 +9754,11 @@
       <c r="I259" t="n">
         <v>0</v>
       </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
@@ -8495,6 +9790,11 @@
       <c r="I260" t="n">
         <v>0</v>
       </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="n">
@@ -8526,6 +9826,11 @@
       <c r="I261" t="n">
         <v>0</v>
       </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
@@ -8557,6 +9862,11 @@
       <c r="I262" t="n">
         <v>0</v>
       </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
@@ -8588,6 +9898,11 @@
       <c r="I263" t="n">
         <v>0</v>
       </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
@@ -8619,6 +9934,11 @@
       <c r="I264" t="n">
         <v>0</v>
       </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
@@ -8650,6 +9970,11 @@
       <c r="I265" t="n">
         <v>0</v>
       </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="n">
@@ -8681,6 +10006,11 @@
       <c r="I266" t="n">
         <v>0</v>
       </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
@@ -8712,6 +10042,11 @@
       <c r="I267" t="n">
         <v>0</v>
       </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
@@ -8743,6 +10078,11 @@
       <c r="I268" t="n">
         <v>0</v>
       </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
@@ -8774,6 +10114,11 @@
       <c r="I269" t="n">
         <v>0</v>
       </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
@@ -8805,6 +10150,11 @@
       <c r="I270" t="n">
         <v>0</v>
       </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
@@ -8836,6 +10186,11 @@
       <c r="I271" t="n">
         <v>0</v>
       </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
@@ -8867,6 +10222,11 @@
       <c r="I272" t="n">
         <v>0</v>
       </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
@@ -8898,6 +10258,11 @@
       <c r="I273" t="n">
         <v>0</v>
       </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
@@ -8929,6 +10294,11 @@
       <c r="I274" t="n">
         <v>0</v>
       </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
@@ -8960,6 +10330,11 @@
       <c r="I275" t="n">
         <v>0</v>
       </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="n">
@@ -8991,6 +10366,11 @@
       <c r="I276" t="n">
         <v>0</v>
       </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
@@ -9022,6 +10402,11 @@
       <c r="I277" t="n">
         <v>0</v>
       </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
@@ -9053,6 +10438,11 @@
       <c r="I278" t="n">
         <v>0</v>
       </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
@@ -9084,6 +10474,11 @@
       <c r="I279" t="n">
         <v>1</v>
       </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
@@ -9115,6 +10510,11 @@
       <c r="I280" t="n">
         <v>1</v>
       </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
@@ -9146,6 +10546,11 @@
       <c r="I281" t="n">
         <v>0</v>
       </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
@@ -9177,6 +10582,11 @@
       <c r="I282" t="n">
         <v>1</v>
       </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
@@ -9208,6 +10618,11 @@
       <c r="I283" t="n">
         <v>0</v>
       </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
@@ -9239,6 +10654,11 @@
       <c r="I284" t="n">
         <v>0</v>
       </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
@@ -9270,6 +10690,11 @@
       <c r="I285" t="n">
         <v>0</v>
       </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
@@ -9301,6 +10726,11 @@
       <c r="I286" t="n">
         <v>0</v>
       </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
@@ -9332,6 +10762,11 @@
       <c r="I287" t="n">
         <v>0</v>
       </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
@@ -9363,6 +10798,11 @@
       <c r="I288" t="n">
         <v>0</v>
       </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
@@ -9394,6 +10834,11 @@
       <c r="I289" t="n">
         <v>0</v>
       </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="n">
@@ -9425,6 +10870,11 @@
       <c r="I290" t="n">
         <v>0</v>
       </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
@@ -9456,6 +10906,11 @@
       <c r="I291" t="n">
         <v>1</v>
       </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
@@ -9487,6 +10942,11 @@
       <c r="I292" t="n">
         <v>0</v>
       </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
@@ -9518,6 +10978,11 @@
       <c r="I293" t="n">
         <v>0</v>
       </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
@@ -9549,6 +11014,11 @@
       <c r="I294" t="n">
         <v>0</v>
       </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
@@ -9580,6 +11050,11 @@
       <c r="I295" t="n">
         <v>0</v>
       </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
@@ -9611,6 +11086,11 @@
       <c r="I296" t="n">
         <v>0</v>
       </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
@@ -9642,6 +11122,11 @@
       <c r="I297" t="n">
         <v>0</v>
       </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="n">
@@ -9673,6 +11158,11 @@
       <c r="I298" t="n">
         <v>0</v>
       </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
@@ -9704,6 +11194,11 @@
       <c r="I299" t="n">
         <v>0</v>
       </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
@@ -9735,6 +11230,11 @@
       <c r="I300" t="n">
         <v>1</v>
       </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
@@ -9766,6 +11266,11 @@
       <c r="I301" t="n">
         <v>0</v>
       </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="n">
@@ -9797,6 +11302,11 @@
       <c r="I302" t="n">
         <v>1</v>
       </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
@@ -9828,6 +11338,11 @@
       <c r="I303" t="n">
         <v>0</v>
       </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
@@ -9859,6 +11374,11 @@
       <c r="I304" t="n">
         <v>0</v>
       </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
@@ -9890,6 +11410,11 @@
       <c r="I305" t="n">
         <v>0</v>
       </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
@@ -9921,6 +11446,11 @@
       <c r="I306" t="n">
         <v>0</v>
       </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
@@ -9952,6 +11482,11 @@
       <c r="I307" t="n">
         <v>0</v>
       </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
@@ -9983,6 +11518,11 @@
       <c r="I308" t="n">
         <v>0</v>
       </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
@@ -10014,6 +11554,11 @@
       <c r="I309" t="n">
         <v>0</v>
       </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
@@ -10045,6 +11590,11 @@
       <c r="I310" t="n">
         <v>0</v>
       </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
@@ -10076,6 +11626,11 @@
       <c r="I311" t="n">
         <v>1</v>
       </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="n">
@@ -10107,6 +11662,11 @@
       <c r="I312" t="n">
         <v>0</v>
       </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="n">
@@ -10138,6 +11698,11 @@
       <c r="I313" t="n">
         <v>0</v>
       </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="n">
@@ -10169,6 +11734,11 @@
       <c r="I314" t="n">
         <v>0</v>
       </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="n">
@@ -10200,6 +11770,11 @@
       <c r="I315" t="n">
         <v>0</v>
       </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="n">
@@ -10231,6 +11806,11 @@
       <c r="I316" t="n">
         <v>0</v>
       </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="n">
@@ -10262,6 +11842,11 @@
       <c r="I317" t="n">
         <v>0</v>
       </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="n">
@@ -10293,6 +11878,11 @@
       <c r="I318" t="n">
         <v>0</v>
       </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="n">
@@ -10324,6 +11914,11 @@
       <c r="I319" t="n">
         <v>0</v>
       </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="n">
@@ -10355,6 +11950,11 @@
       <c r="I320" t="n">
         <v>0</v>
       </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="n">
@@ -10386,6 +11986,11 @@
       <c r="I321" t="n">
         <v>0</v>
       </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="n">
@@ -10417,6 +12022,11 @@
       <c r="I322" t="n">
         <v>0</v>
       </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="n">
@@ -10448,6 +12058,11 @@
       <c r="I323" t="n">
         <v>0</v>
       </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="n">
@@ -10479,6 +12094,11 @@
       <c r="I324" t="n">
         <v>0</v>
       </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="n">
@@ -10510,6 +12130,11 @@
       <c r="I325" t="n">
         <v>0</v>
       </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="n">
@@ -10541,6 +12166,11 @@
       <c r="I326" t="n">
         <v>0</v>
       </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="n">
@@ -10572,6 +12202,11 @@
       <c r="I327" t="n">
         <v>0</v>
       </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="n">
@@ -10603,6 +12238,11 @@
       <c r="I328" t="n">
         <v>0</v>
       </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="n">
@@ -10634,6 +12274,11 @@
       <c r="I329" t="n">
         <v>0</v>
       </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="n">
@@ -10665,6 +12310,11 @@
       <c r="I330" t="n">
         <v>0</v>
       </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="n">
@@ -10696,6 +12346,11 @@
       <c r="I331" t="n">
         <v>0</v>
       </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="n">
@@ -10727,6 +12382,11 @@
       <c r="I332" t="n">
         <v>0</v>
       </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="n">
@@ -10758,6 +12418,11 @@
       <c r="I333" t="n">
         <v>0</v>
       </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="n">
@@ -10789,6 +12454,11 @@
       <c r="I334" t="n">
         <v>0</v>
       </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="n">
@@ -10820,6 +12490,11 @@
       <c r="I335" t="n">
         <v>0</v>
       </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="n">
@@ -10851,6 +12526,11 @@
       <c r="I336" t="n">
         <v>0</v>
       </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="n">
@@ -10882,6 +12562,11 @@
       <c r="I337" t="n">
         <v>0</v>
       </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="n">
@@ -10913,6 +12598,11 @@
       <c r="I338" t="n">
         <v>0</v>
       </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="n">
@@ -10944,6 +12634,11 @@
       <c r="I339" t="n">
         <v>0</v>
       </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="n">
@@ -10975,6 +12670,11 @@
       <c r="I340" t="n">
         <v>0</v>
       </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="n">
@@ -11006,6 +12706,11 @@
       <c r="I341" t="n">
         <v>0</v>
       </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="n">
@@ -11037,6 +12742,11 @@
       <c r="I342" t="n">
         <v>0</v>
       </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="n">
@@ -11068,6 +12778,11 @@
       <c r="I343" t="n">
         <v>0</v>
       </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="n">
@@ -11099,6 +12814,11 @@
       <c r="I344" t="n">
         <v>0</v>
       </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="n">
@@ -11130,6 +12850,11 @@
       <c r="I345" t="n">
         <v>0</v>
       </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="n">
@@ -11161,6 +12886,11 @@
       <c r="I346" t="n">
         <v>0</v>
       </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="n">
@@ -11192,6 +12922,11 @@
       <c r="I347" t="n">
         <v>0</v>
       </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="n">
@@ -11223,6 +12958,11 @@
       <c r="I348" t="n">
         <v>0</v>
       </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="n">
@@ -11254,6 +12994,11 @@
       <c r="I349" t="n">
         <v>0</v>
       </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="n">
@@ -11285,6 +13030,11 @@
       <c r="I350" t="n">
         <v>0</v>
       </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="n">
@@ -11316,6 +13066,11 @@
       <c r="I351" t="n">
         <v>0</v>
       </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="n">
@@ -11347,6 +13102,11 @@
       <c r="I352" t="n">
         <v>0</v>
       </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="n">
@@ -11378,6 +13138,11 @@
       <c r="I353" t="n">
         <v>0</v>
       </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="n">
@@ -11409,6 +13174,11 @@
       <c r="I354" t="n">
         <v>0</v>
       </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="n">
@@ -11440,6 +13210,11 @@
       <c r="I355" t="n">
         <v>0</v>
       </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="n">
@@ -11471,6 +13246,11 @@
       <c r="I356" t="n">
         <v>0</v>
       </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="n">
@@ -11502,6 +13282,11 @@
       <c r="I357" t="n">
         <v>0</v>
       </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="n">
@@ -11533,6 +13318,11 @@
       <c r="I358" t="n">
         <v>0</v>
       </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="n">
@@ -11564,6 +13354,11 @@
       <c r="I359" t="n">
         <v>0</v>
       </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="n">
@@ -11595,6 +13390,11 @@
       <c r="I360" t="n">
         <v>0</v>
       </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="n">
@@ -11626,6 +13426,11 @@
       <c r="I361" t="n">
         <v>0</v>
       </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="n">
@@ -11657,6 +13462,11 @@
       <c r="I362" t="n">
         <v>0</v>
       </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="n">
@@ -11688,6 +13498,11 @@
       <c r="I363" t="n">
         <v>0</v>
       </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="n">
@@ -11719,6 +13534,11 @@
       <c r="I364" t="n">
         <v>0</v>
       </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="n">
@@ -11750,6 +13570,11 @@
       <c r="I365" t="n">
         <v>0</v>
       </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="n">
@@ -11781,6 +13606,11 @@
       <c r="I366" t="n">
         <v>0</v>
       </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="n">
@@ -11812,6 +13642,11 @@
       <c r="I367" t="n">
         <v>0</v>
       </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="n">
@@ -11843,6 +13678,11 @@
       <c r="I368" t="n">
         <v>0</v>
       </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="n">
@@ -11874,6 +13714,11 @@
       <c r="I369" t="n">
         <v>0</v>
       </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="n">
@@ -11905,6 +13750,11 @@
       <c r="I370" t="n">
         <v>0</v>
       </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="n">
@@ -11936,6 +13786,11 @@
       <c r="I371" t="n">
         <v>0</v>
       </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="1" t="n">
@@ -11967,6 +13822,11 @@
       <c r="I372" t="n">
         <v>0</v>
       </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="n">
@@ -11998,6 +13858,11 @@
       <c r="I373" t="n">
         <v>0</v>
       </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="1" t="n">
@@ -12029,6 +13894,11 @@
       <c r="I374" t="n">
         <v>0</v>
       </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
@@ -12060,6 +13930,11 @@
       <c r="I375" t="n">
         <v>0</v>
       </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
@@ -12091,6 +13966,11 @@
       <c r="I376" t="n">
         <v>0</v>
       </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="n">
@@ -12122,6 +14002,11 @@
       <c r="I377" t="n">
         <v>0</v>
       </c>
+      <c r="J377" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="1" t="n">
@@ -12153,6 +14038,11 @@
       <c r="I378" t="n">
         <v>0</v>
       </c>
+      <c r="J378" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
@@ -12184,6 +14074,11 @@
       <c r="I379" t="n">
         <v>0</v>
       </c>
+      <c r="J379" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="1" t="n">
@@ -12215,6 +14110,11 @@
       <c r="I380" t="n">
         <v>0</v>
       </c>
+      <c r="J380" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="n">
@@ -12246,6 +14146,11 @@
       <c r="I381" t="n">
         <v>0</v>
       </c>
+      <c r="J381" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="n">
@@ -12277,6 +14182,11 @@
       <c r="I382" t="n">
         <v>0</v>
       </c>
+      <c r="J382" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="n">
@@ -12308,6 +14218,11 @@
       <c r="I383" t="n">
         <v>0</v>
       </c>
+      <c r="J383" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="n">
@@ -12339,6 +14254,11 @@
       <c r="I384" t="n">
         <v>0</v>
       </c>
+      <c r="J384" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="1" t="n">
@@ -12370,6 +14290,11 @@
       <c r="I385" t="n">
         <v>0</v>
       </c>
+      <c r="J385" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="n">
@@ -12401,6 +14326,11 @@
       <c r="I386" t="n">
         <v>0</v>
       </c>
+      <c r="J386" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="1" t="n">
@@ -12432,6 +14362,11 @@
       <c r="I387" t="n">
         <v>0</v>
       </c>
+      <c r="J387" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="n">
@@ -12463,6 +14398,11 @@
       <c r="I388" t="n">
         <v>0</v>
       </c>
+      <c r="J388" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="n">
@@ -12494,6 +14434,11 @@
       <c r="I389" t="n">
         <v>0</v>
       </c>
+      <c r="J389" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="1" t="n">
@@ -12525,6 +14470,11 @@
       <c r="I390" t="n">
         <v>0</v>
       </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="1" t="n">
@@ -12556,6 +14506,11 @@
       <c r="I391" t="n">
         <v>0</v>
       </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="1" t="n">
@@ -12587,6 +14542,11 @@
       <c r="I392" t="n">
         <v>0</v>
       </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="1" t="n">
@@ -12618,6 +14578,11 @@
       <c r="I393" t="n">
         <v>0</v>
       </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="1" t="n">
@@ -12649,6 +14614,11 @@
       <c r="I394" t="n">
         <v>0</v>
       </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="1" t="n">
@@ -12680,6 +14650,11 @@
       <c r="I395" t="n">
         <v>0</v>
       </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="1" t="n">
@@ -12711,6 +14686,11 @@
       <c r="I396" t="n">
         <v>0</v>
       </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="1" t="n">
@@ -12742,6 +14722,11 @@
       <c r="I397" t="n">
         <v>0</v>
       </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="1" t="n">
@@ -12773,6 +14758,11 @@
       <c r="I398" t="n">
         <v>0</v>
       </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="1" t="n">
@@ -12804,6 +14794,11 @@
       <c r="I399" t="n">
         <v>0</v>
       </c>
+      <c r="J399" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="1" t="n">
@@ -12835,6 +14830,11 @@
       <c r="I400" t="n">
         <v>0</v>
       </c>
+      <c r="J400" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="1" t="n">
@@ -12866,6 +14866,11 @@
       <c r="I401" t="n">
         <v>0</v>
       </c>
+      <c r="J401" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="1" t="n">
@@ -12897,6 +14902,11 @@
       <c r="I402" t="n">
         <v>0</v>
       </c>
+      <c r="J402" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="1" t="n">
@@ -12928,6 +14938,11 @@
       <c r="I403" t="n">
         <v>0</v>
       </c>
+      <c r="J403" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="1" t="n">
@@ -12959,6 +14974,11 @@
       <c r="I404" t="n">
         <v>0</v>
       </c>
+      <c r="J404" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="1" t="n">
@@ -12990,6 +15010,11 @@
       <c r="I405" t="n">
         <v>0</v>
       </c>
+      <c r="J405" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="1" t="n">
@@ -13021,6 +15046,11 @@
       <c r="I406" t="n">
         <v>0</v>
       </c>
+      <c r="J406" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="1" t="n">
@@ -13052,6 +15082,11 @@
       <c r="I407" t="n">
         <v>0</v>
       </c>
+      <c r="J407" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="1" t="n">
@@ -13083,6 +15118,11 @@
       <c r="I408" t="n">
         <v>0</v>
       </c>
+      <c r="J408" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="1" t="n">
@@ -13114,6 +15154,11 @@
       <c r="I409" t="n">
         <v>0</v>
       </c>
+      <c r="J409" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="1" t="n">
@@ -13145,6 +15190,11 @@
       <c r="I410" t="n">
         <v>0</v>
       </c>
+      <c r="J410" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="1" t="n">
@@ -13176,6 +15226,11 @@
       <c r="I411" t="n">
         <v>0</v>
       </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="1" t="n">
@@ -13207,6 +15262,11 @@
       <c r="I412" t="n">
         <v>0</v>
       </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="1" t="n">
@@ -13238,6 +15298,11 @@
       <c r="I413" t="n">
         <v>0</v>
       </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="1" t="n">
@@ -13269,6 +15334,11 @@
       <c r="I414" t="n">
         <v>0</v>
       </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="1" t="n">
@@ -13300,6 +15370,11 @@
       <c r="I415" t="n">
         <v>0</v>
       </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="1" t="n">
@@ -13331,6 +15406,11 @@
       <c r="I416" t="n">
         <v>0</v>
       </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="1" t="n">
@@ -13362,6 +15442,11 @@
       <c r="I417" t="n">
         <v>0</v>
       </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="1" t="n">
@@ -13393,6 +15478,11 @@
       <c r="I418" t="n">
         <v>0</v>
       </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="1" t="n">
@@ -13424,6 +15514,11 @@
       <c r="I419" t="n">
         <v>0</v>
       </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="1" t="n">
@@ -13455,6 +15550,11 @@
       <c r="I420" t="n">
         <v>0</v>
       </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="1" t="n">
@@ -13486,6 +15586,11 @@
       <c r="I421" t="n">
         <v>0</v>
       </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="1" t="n">
@@ -13517,6 +15622,11 @@
       <c r="I422" t="n">
         <v>0</v>
       </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="1" t="n">
@@ -13548,6 +15658,11 @@
       <c r="I423" t="n">
         <v>0</v>
       </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="1" t="n">
@@ -13579,6 +15694,11 @@
       <c r="I424" t="n">
         <v>0</v>
       </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="1" t="n">
@@ -13610,6 +15730,11 @@
       <c r="I425" t="n">
         <v>0</v>
       </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="1" t="n">
@@ -13641,6 +15766,11 @@
       <c r="I426" t="n">
         <v>0</v>
       </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="1" t="n">
@@ -13672,6 +15802,11 @@
       <c r="I427" t="n">
         <v>0</v>
       </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="1" t="n">
@@ -13703,6 +15838,11 @@
       <c r="I428" t="n">
         <v>0</v>
       </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="1" t="n">
@@ -13734,6 +15874,11 @@
       <c r="I429" t="n">
         <v>0</v>
       </c>
+      <c r="J429" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="1" t="n">
@@ -13765,6 +15910,11 @@
       <c r="I430" t="n">
         <v>0</v>
       </c>
+      <c r="J430" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="1" t="n">
@@ -13796,6 +15946,11 @@
       <c r="I431" t="n">
         <v>0</v>
       </c>
+      <c r="J431" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="1" t="n">
@@ -13827,6 +15982,11 @@
       <c r="I432" t="n">
         <v>0</v>
       </c>
+      <c r="J432" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="1" t="n">
@@ -13858,6 +16018,11 @@
       <c r="I433" t="n">
         <v>0</v>
       </c>
+      <c r="J433" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="1" t="n">
@@ -13889,6 +16054,11 @@
       <c r="I434" t="n">
         <v>0</v>
       </c>
+      <c r="J434" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="1" t="n">
@@ -13920,6 +16090,11 @@
       <c r="I435" t="n">
         <v>0</v>
       </c>
+      <c r="J435" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="1" t="n">
@@ -13951,6 +16126,11 @@
       <c r="I436" t="n">
         <v>0</v>
       </c>
+      <c r="J436" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="1" t="n">
@@ -13982,6 +16162,11 @@
       <c r="I437" t="n">
         <v>0</v>
       </c>
+      <c r="J437" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="1" t="n">
@@ -14013,6 +16198,11 @@
       <c r="I438" t="n">
         <v>0</v>
       </c>
+      <c r="J438" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="1" t="n">
@@ -14044,6 +16234,11 @@
       <c r="I439" t="n">
         <v>0</v>
       </c>
+      <c r="J439" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="1" t="n">
@@ -14075,6 +16270,11 @@
       <c r="I440" t="n">
         <v>0</v>
       </c>
+      <c r="J440" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="1" t="n">
@@ -14106,6 +16306,11 @@
       <c r="I441" t="n">
         <v>0</v>
       </c>
+      <c r="J441" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="1" t="n">
@@ -14137,6 +16342,11 @@
       <c r="I442" t="n">
         <v>0</v>
       </c>
+      <c r="J442" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="1" t="n">
@@ -14168,6 +16378,11 @@
       <c r="I443" t="n">
         <v>0</v>
       </c>
+      <c r="J443" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="1" t="n">
@@ -14199,6 +16414,11 @@
       <c r="I444" t="n">
         <v>0</v>
       </c>
+      <c r="J444" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="1" t="n">
@@ -14230,6 +16450,11 @@
       <c r="I445" t="n">
         <v>0</v>
       </c>
+      <c r="J445" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="1" t="n">
@@ -14261,6 +16486,11 @@
       <c r="I446" t="n">
         <v>0</v>
       </c>
+      <c r="J446" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="1" t="n">
@@ -14292,6 +16522,11 @@
       <c r="I447" t="n">
         <v>0</v>
       </c>
+      <c r="J447" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" s="1" t="n">
@@ -14323,6 +16558,11 @@
       <c r="I448" t="n">
         <v>0</v>
       </c>
+      <c r="J448" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="1" t="n">
@@ -14354,6 +16594,11 @@
       <c r="I449" t="n">
         <v>0</v>
       </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="1" t="n">
@@ -14385,6 +16630,11 @@
       <c r="I450" t="n">
         <v>0</v>
       </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="1" t="n">
@@ -14416,6 +16666,11 @@
       <c r="I451" t="n">
         <v>0</v>
       </c>
+      <c r="J451" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" s="1" t="n">
@@ -14447,6 +16702,11 @@
       <c r="I452" t="n">
         <v>0</v>
       </c>
+      <c r="J452" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="1" t="n">
@@ -14478,6 +16738,11 @@
       <c r="I453" t="n">
         <v>0</v>
       </c>
+      <c r="J453" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="1" t="n">
@@ -14509,6 +16774,11 @@
       <c r="I454" t="n">
         <v>0</v>
       </c>
+      <c r="J454" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" s="1" t="n">
@@ -14540,6 +16810,11 @@
       <c r="I455" t="n">
         <v>0</v>
       </c>
+      <c r="J455" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="1" t="n">
@@ -14571,6 +16846,11 @@
       <c r="I456" t="n">
         <v>0</v>
       </c>
+      <c r="J456" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="1" t="n">
@@ -14602,6 +16882,11 @@
       <c r="I457" t="n">
         <v>0</v>
       </c>
+      <c r="J457" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="1" t="n">
@@ -14633,6 +16918,11 @@
       <c r="I458" t="n">
         <v>0</v>
       </c>
+      <c r="J458" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="1" t="n">
@@ -14664,6 +16954,11 @@
       <c r="I459" t="n">
         <v>0</v>
       </c>
+      <c r="J459" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" s="1" t="n">
@@ -14695,6 +16990,11 @@
       <c r="I460" t="n">
         <v>0</v>
       </c>
+      <c r="J460" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="1" t="n">
@@ -14726,6 +17026,11 @@
       <c r="I461" t="n">
         <v>0</v>
       </c>
+      <c r="J461" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" s="1" t="n">
@@ -14757,6 +17062,11 @@
       <c r="I462" t="n">
         <v>0</v>
       </c>
+      <c r="J462" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" s="1" t="n">
@@ -14788,6 +17098,11 @@
       <c r="I463" t="n">
         <v>0</v>
       </c>
+      <c r="J463" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" s="1" t="n">
@@ -14819,6 +17134,11 @@
       <c r="I464" t="n">
         <v>0</v>
       </c>
+      <c r="J464" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" s="1" t="n">
@@ -14850,6 +17170,11 @@
       <c r="I465" t="n">
         <v>0</v>
       </c>
+      <c r="J465" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" s="1" t="n">
@@ -14881,6 +17206,11 @@
       <c r="I466" t="n">
         <v>0</v>
       </c>
+      <c r="J466" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" s="1" t="n">
@@ -14912,6 +17242,11 @@
       <c r="I467" t="n">
         <v>0</v>
       </c>
+      <c r="J467" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="1" t="n">
@@ -14943,6 +17278,11 @@
       <c r="I468" t="n">
         <v>0</v>
       </c>
+      <c r="J468" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" s="1" t="n">
@@ -14974,6 +17314,11 @@
       <c r="I469" t="n">
         <v>0</v>
       </c>
+      <c r="J469" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="1" t="n">
@@ -15005,6 +17350,11 @@
       <c r="I470" t="n">
         <v>0</v>
       </c>
+      <c r="J470" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="1" t="n">
@@ -15036,6 +17386,11 @@
       <c r="I471" t="n">
         <v>0</v>
       </c>
+      <c r="J471" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="1" t="n">
@@ -15067,6 +17422,11 @@
       <c r="I472" t="n">
         <v>0</v>
       </c>
+      <c r="J472" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="1" t="n">
@@ -15098,6 +17458,11 @@
       <c r="I473" t="n">
         <v>0</v>
       </c>
+      <c r="J473" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="1" t="n">
@@ -15129,6 +17494,11 @@
       <c r="I474" t="n">
         <v>0</v>
       </c>
+      <c r="J474" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" s="1" t="n">
@@ -15160,6 +17530,11 @@
       <c r="I475" t="n">
         <v>0</v>
       </c>
+      <c r="J475" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" s="1" t="n">
@@ -15191,6 +17566,11 @@
       <c r="I476" t="n">
         <v>0</v>
       </c>
+      <c r="J476" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="1" t="n">
@@ -15222,6 +17602,11 @@
       <c r="I477" t="n">
         <v>0</v>
       </c>
+      <c r="J477" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" s="1" t="n">
@@ -15253,6 +17638,11 @@
       <c r="I478" t="n">
         <v>0</v>
       </c>
+      <c r="J478" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="1" t="n">
@@ -15284,6 +17674,11 @@
       <c r="I479" t="n">
         <v>0</v>
       </c>
+      <c r="J479" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="1" t="n">
@@ -15315,6 +17710,11 @@
       <c r="I480" t="n">
         <v>0</v>
       </c>
+      <c r="J480" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" s="1" t="n">
@@ -15346,6 +17746,11 @@
       <c r="I481" t="n">
         <v>0</v>
       </c>
+      <c r="J481" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" s="1" t="n">
@@ -15377,6 +17782,11 @@
       <c r="I482" t="n">
         <v>0</v>
       </c>
+      <c r="J482" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" s="1" t="n">
@@ -15408,6 +17818,11 @@
       <c r="I483" t="n">
         <v>0</v>
       </c>
+      <c r="J483" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" s="1" t="n">
@@ -15439,6 +17854,11 @@
       <c r="I484" t="n">
         <v>0</v>
       </c>
+      <c r="J484" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" s="1" t="n">
@@ -15470,6 +17890,11 @@
       <c r="I485" t="n">
         <v>0</v>
       </c>
+      <c r="J485" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="1" t="n">
@@ -15500,6 +17925,11 @@
       </c>
       <c r="I486" t="n">
         <v>0</v>
+      </c>
+      <c r="J486" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/report.xlsx
+++ b/report.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J486"/>
+  <dimension ref="A1:J1143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,7 +504,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -576,7 +576,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -900,7 +900,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -936,7 +936,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1368,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -1440,7 +1440,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1512,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -1764,7 +1764,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -1836,7 +1836,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2232,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -2268,7 +2268,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -2448,7 +2448,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2772,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -2808,7 +2808,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -2844,7 +2844,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -2880,7 +2880,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -2916,7 +2916,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -2952,7 +2952,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3096,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -3312,7 +3312,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -3528,7 +3528,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -3564,7 +3564,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -3672,7 +3672,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3708,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -3780,7 +3780,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -3852,7 +3852,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3888,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -3996,7 +3996,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -4032,7 +4032,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -4068,7 +4068,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -4320,7 +4320,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -4464,7 +4464,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -4572,7 +4572,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -4788,7 +4788,7 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -4824,7 +4824,7 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -4932,7 +4932,7 @@
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -4968,7 +4968,7 @@
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5040,7 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -5076,7 +5076,7 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -5256,7 +5256,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -5328,7 +5328,7 @@
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -5436,7 +5436,7 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -5580,7 +5580,7 @@
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -5688,7 +5688,7 @@
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5796,7 @@
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -5940,7 +5940,7 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -5976,7 +5976,7 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6084,7 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6120,7 @@
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -6336,7 +6336,7 @@
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -6372,7 +6372,7 @@
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -6408,7 +6408,7 @@
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6480,7 @@
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -6624,7 +6624,7 @@
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -6660,7 +6660,7 @@
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -6732,7 +6732,7 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6768,7 @@
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -6876,7 +6876,7 @@
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -6948,7 +6948,7 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -6984,7 +6984,7 @@
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -7092,7 +7092,7 @@
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -7308,7 +7308,7 @@
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -7344,7 +7344,7 @@
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -7488,7 +7488,7 @@
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -7524,7 +7524,7 @@
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -7560,7 +7560,7 @@
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -7596,7 +7596,7 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -7632,7 +7632,7 @@
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -7668,7 +7668,7 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -7704,7 +7704,7 @@
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -7740,7 +7740,7 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -7776,7 +7776,7 @@
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -7848,7 +7848,7 @@
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -7884,7 +7884,7 @@
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -7992,7 +7992,7 @@
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -8028,7 +8028,7 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -8100,7 +8100,7 @@
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -8136,7 +8136,7 @@
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -8172,7 +8172,7 @@
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8352,7 @@
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -8388,7 +8388,7 @@
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -8460,7 +8460,7 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -8496,7 +8496,7 @@
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -8532,7 +8532,7 @@
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -8568,7 +8568,7 @@
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -8640,7 +8640,7 @@
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -8676,7 +8676,7 @@
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -8712,7 +8712,7 @@
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -8748,7 +8748,7 @@
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="J233" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -8856,7 +8856,7 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -8892,7 +8892,7 @@
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -8928,7 +8928,7 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -8964,7 +8964,7 @@
       </c>
       <c r="J237" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -9000,7 +9000,7 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="J239" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -9108,7 +9108,7 @@
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -9144,7 +9144,7 @@
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -9180,7 +9180,7 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -9216,7 +9216,7 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -9252,7 +9252,7 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -9288,7 +9288,7 @@
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -9324,7 +9324,7 @@
       </c>
       <c r="J247" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -9360,7 +9360,7 @@
       </c>
       <c r="J248" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -9396,7 +9396,7 @@
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -9432,7 +9432,7 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -9504,7 +9504,7 @@
       </c>
       <c r="J252" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -9540,7 +9540,7 @@
       </c>
       <c r="J253" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -9576,7 +9576,7 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -9684,7 +9684,7 @@
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -9720,7 +9720,7 @@
       </c>
       <c r="J258" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -9756,7 +9756,7 @@
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -9792,7 +9792,7 @@
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -9828,7 +9828,7 @@
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -9864,7 +9864,7 @@
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -9900,7 +9900,7 @@
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -9936,7 +9936,7 @@
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -9972,7 +9972,7 @@
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -10008,7 +10008,7 @@
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -10044,7 +10044,7 @@
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -10116,7 +10116,7 @@
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -10152,7 +10152,7 @@
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -10188,7 +10188,7 @@
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -10224,7 +10224,7 @@
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -10332,7 +10332,7 @@
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -10404,7 +10404,7 @@
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -10440,7 +10440,7 @@
       </c>
       <c r="J278" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -10476,7 +10476,7 @@
       </c>
       <c r="J279" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -10512,7 +10512,7 @@
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="J282" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -10692,7 +10692,7 @@
       </c>
       <c r="J285" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -10728,7 +10728,7 @@
       </c>
       <c r="J286" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -10836,7 +10836,7 @@
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -10872,7 +10872,7 @@
       </c>
       <c r="J290" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -10908,7 +10908,7 @@
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -10944,7 +10944,7 @@
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -10980,7 +10980,7 @@
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -11016,7 +11016,7 @@
       </c>
       <c r="J294" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -11052,7 +11052,7 @@
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -11088,7 +11088,7 @@
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -11124,7 +11124,7 @@
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -11160,7 +11160,7 @@
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -11196,7 +11196,7 @@
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -11232,7 +11232,7 @@
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -11268,7 +11268,7 @@
       </c>
       <c r="J301" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -11304,7 +11304,7 @@
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="J303" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -11376,7 +11376,7 @@
       </c>
       <c r="J304" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -11412,7 +11412,7 @@
       </c>
       <c r="J305" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="J306" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -11484,7 +11484,7 @@
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -11520,7 +11520,7 @@
       </c>
       <c r="J308" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -11556,7 +11556,7 @@
       </c>
       <c r="J309" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -11592,7 +11592,7 @@
       </c>
       <c r="J310" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -11628,7 +11628,7 @@
       </c>
       <c r="J311" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11664,7 @@
       </c>
       <c r="J312" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -11700,7 +11700,7 @@
       </c>
       <c r="J313" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -11736,7 +11736,7 @@
       </c>
       <c r="J314" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -11772,7 +11772,7 @@
       </c>
       <c r="J315" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -11808,7 +11808,7 @@
       </c>
       <c r="J316" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="J317" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -11880,7 +11880,7 @@
       </c>
       <c r="J318" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -11916,7 +11916,7 @@
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -11952,7 +11952,7 @@
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -11988,7 +11988,7 @@
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -12024,7 +12024,7 @@
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -12060,7 +12060,7 @@
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -12132,7 +12132,7 @@
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -12168,7 +12168,7 @@
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -12204,7 +12204,7 @@
       </c>
       <c r="J327" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -12240,7 +12240,7 @@
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -12276,7 +12276,7 @@
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -12312,7 +12312,7 @@
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -12348,7 +12348,7 @@
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -12384,7 +12384,7 @@
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -12420,7 +12420,7 @@
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -12456,7 +12456,7 @@
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -12492,7 +12492,7 @@
       </c>
       <c r="J335" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -12528,7 +12528,7 @@
       </c>
       <c r="J336" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -12564,7 +12564,7 @@
       </c>
       <c r="J337" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -12600,7 +12600,7 @@
       </c>
       <c r="J338" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -12636,7 +12636,7 @@
       </c>
       <c r="J339" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -12672,7 +12672,7 @@
       </c>
       <c r="J340" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -12708,7 +12708,7 @@
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -12744,7 +12744,7 @@
       </c>
       <c r="J342" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -12780,7 +12780,7 @@
       </c>
       <c r="J343" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -12816,7 +12816,7 @@
       </c>
       <c r="J344" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -12852,7 +12852,7 @@
       </c>
       <c r="J345" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="J346" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="J347" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -12960,7 +12960,7 @@
       </c>
       <c r="J348" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -12996,7 +12996,7 @@
       </c>
       <c r="J349" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -13032,7 +13032,7 @@
       </c>
       <c r="J350" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -13068,7 +13068,7 @@
       </c>
       <c r="J351" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -13104,7 +13104,7 @@
       </c>
       <c r="J352" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -13140,7 +13140,7 @@
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -13176,7 +13176,7 @@
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -13212,7 +13212,7 @@
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -13248,7 +13248,7 @@
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -13284,7 +13284,7 @@
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -13356,7 +13356,7 @@
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -13392,7 +13392,7 @@
       </c>
       <c r="J360" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -13428,7 +13428,7 @@
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -13464,7 +13464,7 @@
       </c>
       <c r="J362" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -13500,7 +13500,7 @@
       </c>
       <c r="J363" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -13536,7 +13536,7 @@
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -13572,7 +13572,7 @@
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -13608,7 +13608,7 @@
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -13644,7 +13644,7 @@
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -13680,7 +13680,7 @@
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -13716,7 +13716,7 @@
       </c>
       <c r="J369" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -13752,7 +13752,7 @@
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -13788,7 +13788,7 @@
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -13824,7 +13824,7 @@
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -13860,7 +13860,7 @@
       </c>
       <c r="J373" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -13896,7 +13896,7 @@
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="J376" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -14004,7 +14004,7 @@
       </c>
       <c r="J377" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -14040,7 +14040,7 @@
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -14076,7 +14076,7 @@
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="J380" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -14148,7 +14148,7 @@
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -14184,7 +14184,7 @@
       </c>
       <c r="J382" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -14220,7 +14220,7 @@
       </c>
       <c r="J383" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -14256,7 +14256,7 @@
       </c>
       <c r="J384" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -14292,7 +14292,7 @@
       </c>
       <c r="J385" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -14328,7 +14328,7 @@
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -14364,7 +14364,7 @@
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -14400,7 +14400,7 @@
       </c>
       <c r="J388" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -14436,7 +14436,7 @@
       </c>
       <c r="J389" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -14472,7 +14472,7 @@
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -14508,7 +14508,7 @@
       </c>
       <c r="J391" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -14544,7 +14544,7 @@
       </c>
       <c r="J392" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -14580,7 +14580,7 @@
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -14616,7 +14616,7 @@
       </c>
       <c r="J394" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -14652,7 +14652,7 @@
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -14688,7 +14688,7 @@
       </c>
       <c r="J396" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -14724,7 +14724,7 @@
       </c>
       <c r="J397" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -14760,7 +14760,7 @@
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14796,7 @@
       </c>
       <c r="J399" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -14832,7 +14832,7 @@
       </c>
       <c r="J400" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -14868,7 +14868,7 @@
       </c>
       <c r="J401" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -14904,7 +14904,7 @@
       </c>
       <c r="J402" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -14940,7 +14940,7 @@
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -14976,7 +14976,7 @@
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -15012,7 +15012,7 @@
       </c>
       <c r="J405" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -15048,7 +15048,7 @@
       </c>
       <c r="J406" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -15084,7 +15084,7 @@
       </c>
       <c r="J407" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -15120,7 +15120,7 @@
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -15156,7 +15156,7 @@
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -15192,7 +15192,7 @@
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -15228,7 +15228,7 @@
       </c>
       <c r="J411" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -15264,7 +15264,7 @@
       </c>
       <c r="J412" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -15300,7 +15300,7 @@
       </c>
       <c r="J413" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -15372,7 +15372,7 @@
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -15408,7 +15408,7 @@
       </c>
       <c r="J416" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -15444,7 +15444,7 @@
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -15480,7 +15480,7 @@
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -15516,7 +15516,7 @@
       </c>
       <c r="J419" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -15552,7 +15552,7 @@
       </c>
       <c r="J420" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -15588,7 +15588,7 @@
       </c>
       <c r="J421" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -15624,7 +15624,7 @@
       </c>
       <c r="J422" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -15660,7 +15660,7 @@
       </c>
       <c r="J423" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -15696,7 +15696,7 @@
       </c>
       <c r="J424" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -15732,7 +15732,7 @@
       </c>
       <c r="J425" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -15768,7 +15768,7 @@
       </c>
       <c r="J426" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -15804,7 +15804,7 @@
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -15840,7 +15840,7 @@
       </c>
       <c r="J428" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -15876,7 +15876,7 @@
       </c>
       <c r="J429" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -15912,7 +15912,7 @@
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -15948,7 +15948,7 @@
       </c>
       <c r="J431" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -15984,7 +15984,7 @@
       </c>
       <c r="J432" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -16020,7 +16020,7 @@
       </c>
       <c r="J433" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -16056,7 +16056,7 @@
       </c>
       <c r="J434" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -16092,7 +16092,7 @@
       </c>
       <c r="J435" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -16128,7 +16128,7 @@
       </c>
       <c r="J436" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -16164,7 +16164,7 @@
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -16200,7 +16200,7 @@
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -16236,7 +16236,7 @@
       </c>
       <c r="J439" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -16272,7 +16272,7 @@
       </c>
       <c r="J440" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -16308,7 +16308,7 @@
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -16344,7 +16344,7 @@
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -16380,7 +16380,7 @@
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -16416,7 +16416,7 @@
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -16452,7 +16452,7 @@
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -16488,7 +16488,7 @@
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -16524,7 +16524,7 @@
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -16560,7 +16560,7 @@
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -16596,7 +16596,7 @@
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -16632,7 +16632,7 @@
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -16668,7 +16668,7 @@
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -16704,7 +16704,7 @@
       </c>
       <c r="J452" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -16740,7 +16740,7 @@
       </c>
       <c r="J453" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -16776,7 +16776,7 @@
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -16812,7 +16812,7 @@
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -16848,7 +16848,7 @@
       </c>
       <c r="J456" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -16884,7 +16884,7 @@
       </c>
       <c r="J457" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -16920,7 +16920,7 @@
       </c>
       <c r="J458" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -16956,7 +16956,7 @@
       </c>
       <c r="J459" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -17028,7 +17028,7 @@
       </c>
       <c r="J461" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -17064,7 +17064,7 @@
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -17100,7 +17100,7 @@
       </c>
       <c r="J463" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -17136,7 +17136,7 @@
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -17172,7 +17172,7 @@
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -17208,7 +17208,7 @@
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -17244,7 +17244,7 @@
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -17280,7 +17280,7 @@
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -17316,7 +17316,7 @@
       </c>
       <c r="J469" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -17352,7 +17352,7 @@
       </c>
       <c r="J470" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -17388,7 +17388,7 @@
       </c>
       <c r="J471" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -17424,7 +17424,7 @@
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -17460,7 +17460,7 @@
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -17496,7 +17496,7 @@
       </c>
       <c r="J474" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="J475" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -17568,7 +17568,7 @@
       </c>
       <c r="J476" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="J477" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="J478" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -17676,7 +17676,7 @@
       </c>
       <c r="J479" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -17712,7 +17712,7 @@
       </c>
       <c r="J480" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -17748,7 +17748,7 @@
       </c>
       <c r="J481" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -17784,7 +17784,7 @@
       </c>
       <c r="J482" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -17820,7 +17820,7 @@
       </c>
       <c r="J483" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -17856,7 +17856,7 @@
       </c>
       <c r="J484" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="J485" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
         </is>
       </c>
     </row>
@@ -17928,7 +17928,4606 @@
       </c>
       <c r="J486" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="J487" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="J502" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="J503" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="J504" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="J505" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="J506" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="J507" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="J508" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="J509" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="J510" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="J511" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="J512" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="J513" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="J514" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="J515" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="J516" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="J517" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="J518" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="J519" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="J520" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="J521" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="J522" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="J523" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="J524" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="J525" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="J526" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="J527" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="J528" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="J529" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="J530" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="J531" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="J532" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="J533" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="J534" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="J535" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="J536" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="J537" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="J538" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="J539" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="J540" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="J541" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="J542" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="J543" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="J544" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="J545" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="J546" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="J547" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="J575" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="J576" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="J577" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="J578" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="J579" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="J580" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="J581" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="J665" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="J666" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="J667" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="J668" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="J669" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="J670" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="J671" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="J672" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="J673" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="J674" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="J675" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="J676" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="J677" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="J678" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="J679" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="J680" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="J681" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="J682" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="J683" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="J684" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="J685" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="J686" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="J687" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="J688" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="J689" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="J690" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="J691" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="J692" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="J693" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="J694" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="J695" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="J696" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="J697" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="J698" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="J703" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="J704" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="J705" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="J706" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="J707" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="J708" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="J709" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="J711" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="J712" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="J715" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="J718" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="J719" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="J720" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="J721" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="J722" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="J723" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="J724" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="J725" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="J726" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="J727" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="J728" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="J729" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="J730" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="J731" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="J732" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="J733" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="J734" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="J735" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="J736" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="J737" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="J738" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="J739" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="J740" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="J741" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="J742" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="J743" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="J744" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="J745" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="J746" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="J747" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="J748" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="J749" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="J750" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="J751" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="J752" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="J753" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="J754" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="J755" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="J756" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="J757" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="J758" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="J759" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="J760" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="J761" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="J762" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="J763" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="J764" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="J765" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="J766" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="J767" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="J768" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="J769" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="J770" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="J771" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="J772" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="J773" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="J774" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="J775" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="J776" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="J777" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="J778" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="J779" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="J780" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="J781" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="J782" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="J783" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="J784" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="J785" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="J786" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="J787" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="J788" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="J789" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="J790" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="J791" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="J792" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="J793" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="J794" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="J795" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="J796" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="J797" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="J798" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="J799" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="J800" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="J801" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="J802" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="J803" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="J804" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="J805" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="J806" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="J807" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="J808" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="J809" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="J810" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="J811" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="J812" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="J813" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="J814" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="J815" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="J816" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="J817" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="J818" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="J819" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="J820" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="J821" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="J822" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="J823" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="J824" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="J825" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="J826" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="J827" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="J828" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="J829" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="J830" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="J831" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="J832" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="833">
+      <c r="J833" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="J834" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="J835" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="J836" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="J837" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="J838" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="J839" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="J840" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="J841" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="J842" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="J843" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="J844" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="J845" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="J846" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="J847" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="J848" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="J849" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="J850" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="J851" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="J852" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="J853" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="J854" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="J855" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="J856" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="J857" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="J858" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="J859" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="J860" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="J861" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="J862" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="J863" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="J864" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="J865" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="J866" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="J867" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="J868" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="J869" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="J870" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="J871" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="J872" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="J873" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="J874" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="J875" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="J876" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="J877" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="J878" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="J879" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="J880" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="J881" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="J882" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="J883" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="J884" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="J885" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="J886" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="J887" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="J888" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="J889" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="J890" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="J891" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="J892" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="J893" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="J894" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="J895" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="J896" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="J897" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="J898" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="J899" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="J900" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="J901" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="J902" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="J903" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="J904" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="J905" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="J906" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="J907" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="J908" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="J909" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="J910" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="J911" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="J912" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="J913" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="J914" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="J915" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="J916" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="J917" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="J918" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="J919" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="J920" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="J921" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="J922" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="J923" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="J924" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="J925" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="J926" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="J927" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="J928" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="J929" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="J930" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="J931" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="J932" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="J933" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="J934" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="J935" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="J936" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="J937" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="J938" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="J939" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="J940" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="J941" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="J942" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="J943" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="J944" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="J945" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="J946" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="J947" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="J948" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="J949" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="J950" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="J951" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="J952" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="J953" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="J954" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="J955" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="J956" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="J957" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="J958" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="J959" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="J960" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="J961" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="J962" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="J963" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="J964" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="J965" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="J966" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="J967" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="J968" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="J969" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="J970" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="J971" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="J972" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="J973" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="J974" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="J975" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="J976" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="J977" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="J978" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="J979" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="J980" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="J981" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="J982" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="J983" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="J984" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="J985" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="J986" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="J987" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="988">
+      <c r="J988" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="J989" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="J990" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="J991" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="J992" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="J993" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="J994" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="J995" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="J996" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="J997" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="J998" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="J999" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="J1000" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="J1001" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="J1002" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="J1003" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="J1004" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="J1005" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="J1006" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="J1007" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="J1008" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="J1009" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="J1010" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="J1011" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="J1012" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="J1013" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="J1014" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="J1015" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="J1016" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="J1017" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="J1018" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="J1019" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="J1020" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="J1021" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="J1022" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="J1023" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="J1024" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="J1025" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="J1026" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="J1027" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="J1028" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="J1029" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="J1030" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="J1031" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="J1032" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="J1033" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="J1034" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="J1035" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="J1036" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="J1037" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="J1038" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="J1039" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="J1040" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="J1041" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="J1042" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="J1043" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="J1044" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="J1045" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="J1046" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="J1047" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="J1048" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="J1049" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="J1050" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="J1051" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="J1052" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="J1053" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="J1054" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="J1055" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="J1056" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="J1057" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="J1058" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="J1059" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="J1060" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="J1061" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="J1062" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="J1063" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="J1064" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="J1065" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="J1066" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="J1067" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="J1068" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="J1069" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="J1070" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="J1071" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="J1072" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="J1073" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="J1074" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="J1075" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="J1076" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="J1077" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="J1078" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="J1079" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="J1080" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="J1081" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="J1082" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="J1083" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="J1084" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="J1085" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="J1086" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="J1087" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="J1088" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="J1089" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="J1090" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="J1091" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="J1092" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="J1093" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="J1094" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="J1095" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="J1096" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="J1097" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="J1098" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="J1099" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="J1100" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="J1101" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="J1102" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="J1103" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="J1104" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="J1105" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="J1106" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="J1107" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="J1108" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="J1109" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="J1110" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="J1111" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="J1112" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="J1113" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="J1114" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="J1115" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="J1116" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="J1117" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="J1118" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="J1119" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="J1120" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="J1121" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="J1122" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="J1123" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="J1124" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="J1125" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="J1126" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="J1127" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="J1128" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="J1129" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="J1130" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="J1131" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="J1132" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="J1133" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="J1134" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="J1135" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="J1136" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="J1137" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="J1138" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="J1139" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="J1140" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="J1141" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="J1142" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="J1143" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
         </is>
       </c>
     </row>

--- a/report.xlsx
+++ b/report.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Videos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Vault Events" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22534,4 +22535,651 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Session</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Event name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Training data </t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Training Event count</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Training Context</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Production data</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>production Event count</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Production Context</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Accuracy rate</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>FP</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>FN</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Branch</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Session Time Range</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>15 Sep</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Box came out of safe</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>S14, S2, S3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>tavakere</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>10:15 AM - 10:23 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Box opened outside of table</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Box opened(in frames)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>S14, S2, S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Box closed(in frames)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>S14, S2, S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>15 Sep</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Box closed(in frames)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>tavakere</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>10:26 AM - 10:26 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>15 Sep</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Box came out of safe</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>tavakere</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>10:45 AM - 10:47 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Box opened(in frames)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Box closed(in frames)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>15 Sep</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Box opened(in frames)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>tavakere</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>10:49 AM - 10:52 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Box closed(in frames)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>15 Sep</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Box came out of safe</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>tavakere</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>10:55 AM - 11:03 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Box opened(in frames)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Box closed(in frames)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>S3, S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>15 Sep</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Box came out of safe</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>tavakere</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>11:22 AM - 11:37 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Box opened(in frames)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>S4, S5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Box closed(in frames)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>15 Sep</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>S7</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Box opened(in frames)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>tavakere</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>11:40 AM - 11:43 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Box closed(in frames)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/report.xlsx
+++ b/report.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1143"/>
+  <dimension ref="A1:J1879"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22527,6 +22527,5158 @@
     </row>
     <row r="1143">
       <c r="J1143" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="J1144" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="J1145" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="J1146" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="J1147" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="J1148" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="J1149" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="J1150" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="J1151" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="J1152" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="J1153" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="J1154" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="J1155" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="J1156" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="J1157" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="J1158" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="J1159" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="J1160" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="J1161" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="J1162" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="J1163" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="J1164" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="J1165" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="J1166" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="J1167" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="J1168" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="J1169" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="J1170" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="J1171" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="J1172" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="J1173" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="J1174" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="J1175" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="J1176" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="J1177" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="J1178" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="J1179" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="J1180" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="J1181" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="J1182" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="J1183" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="J1184" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="J1185" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="J1186" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="J1187" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="J1188" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="J1189" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="J1190" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="J1191" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="J1192" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="J1193" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="J1194" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="J1195" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="J1196" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="J1197" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="J1198" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="J1199" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="J1200" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="J1201" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="J1202" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="J1203" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="J1204" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="J1205" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="J1206" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="J1207" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="J1208" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="J1209" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="J1210" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="J1211" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="J1212" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="J1213" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="J1214" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="J1215" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="J1216" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="J1217" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="J1218" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="J1219" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="J1220" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="J1221" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="J1222" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="J1223" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="J1224" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="J1225" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="J1226" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="J1227" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="J1228" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="J1229" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="J1230" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="J1231" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="J1232" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="J1233" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="J1234" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="J1235" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="J1236" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="J1237" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="J1238" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="J1239" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="J1240" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="J1241" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="J1242" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="J1243" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="J1244" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="J1245" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="J1246" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="J1247" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="J1248" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="J1249" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="J1250" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="J1251" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="J1252" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="J1253" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="J1254" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="J1255" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="J1256" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="J1257" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="J1258" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="J1259" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="J1260" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="J1261" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="J1262" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="J1263" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="J1264" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="J1265" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="J1266" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="J1267" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="J1268" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="J1269" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="J1270" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="J1271" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="J1272" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="J1273" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="J1274" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="J1275" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="J1276" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="J1277" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="J1278" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="J1279" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="J1280" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="J1281" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="J1282" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="J1283" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="J1284" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="J1285" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="J1286" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="J1287" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="J1288" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="J1289" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="J1290" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="J1291" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="J1292" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="J1293" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="J1294" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="J1295" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="J1296" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="J1297" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="J1298" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="J1299" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="J1300" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="J1301" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="J1302" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="J1303" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="J1304" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="J1305" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="J1306" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="J1307" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="J1308" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="J1309" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="J1310" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="J1311" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="J1312" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="J1313" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="J1314" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="J1315" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="J1316" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="J1317" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="J1318" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="J1319" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="J1320" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="J1321" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="J1322" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="J1323" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="J1324" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="J1325" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="J1326" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="J1327" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="J1328" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="J1329" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="J1330" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="J1331" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="J1332" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="J1333" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="J1334" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="J1335" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="J1336" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="J1337" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="J1338" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="J1339" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="J1340" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="J1341" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="J1342" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="J1343" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="J1344" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="J1345" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="J1346" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="J1347" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="J1348" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="J1349" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="J1350" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="J1351" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="J1352" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="J1353" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="J1354" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="J1355" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="J1356" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="J1357" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="J1358" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="J1359" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="J1360" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="J1361" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="J1362" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="J1363" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="J1364" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="J1365" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="J1366" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="J1367" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="J1368" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="J1369" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="J1370" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="J1371" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="J1372" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="J1373" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="J1374" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="J1375" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="J1376" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="J1377" t="inlineStr">
+        <is>
+          <t>rtnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="J1378" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="J1379" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="J1380" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="J1381" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="J1382" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="J1383" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="J1384" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="J1385" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="J1386" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="J1387" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="J1388" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="J1389" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="J1390" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="J1391" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="J1392" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="J1393" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="J1394" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="J1395" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="J1396" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="J1397" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="J1398" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="J1399" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="J1400" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="J1401" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="J1402" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="J1403" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="J1404" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="J1405" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="J1406" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="J1407" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="J1408" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="J1409" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="J1410" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="J1411" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="J1412" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="J1413" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="J1414" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="J1415" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="J1416" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="J1417" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="J1418" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="J1419" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="J1420" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="J1421" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="J1422" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="J1423" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="J1424" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="J1425" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="J1426" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="J1427" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="J1428" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="J1429" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="J1430" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="J1431" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="J1432" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="J1433" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="J1434" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="J1435" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="J1436" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="J1437" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="J1438" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="J1439" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="J1440" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="J1441" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="J1442" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="J1443" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="J1444" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="J1445" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="J1446" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="J1447" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="J1448" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="J1449" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="J1450" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="J1451" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="J1452" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="J1453" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="J1454" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="J1455" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="J1456" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="J1457" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="J1458" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="J1459" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="J1460" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="J1461" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="J1462" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="J1463" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="J1464" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="J1465" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="J1466" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="J1467" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="J1468" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="J1469" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="J1470" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="J1471" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="J1472" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="J1473" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="J1474" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="J1475" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="J1476" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="J1477" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="J1478" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="J1479" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="J1480" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="J1481" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="J1482" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="J1483" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="J1484" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="J1485" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="J1486" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="J1487" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="J1488" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="J1489" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="J1490" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="J1491" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="J1492" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="J1493" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="J1494" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="J1495" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="J1496" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="J1497" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="J1498" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="J1499" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="J1500" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="J1501" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="J1502" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="J1503" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="J1504" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="J1505" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="J1506" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="J1507" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="J1508" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="J1509" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="J1510" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="J1511" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="J1512" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="J1513" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="J1514" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="J1515" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="J1516" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="J1517" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="J1518" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="J1519" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="J1520" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="J1521" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="J1522" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="J1523" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="J1524" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="J1525" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="J1526" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="J1527" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="J1528" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="J1529" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="J1530" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="J1531" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="J1532" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="J1533" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="J1534" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="J1535" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="J1536" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="J1537" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="J1538" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="J1539" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="J1540" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="J1541" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="J1542" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="J1543" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="J1544" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="J1545" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="J1546" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="J1547" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="J1548" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="J1549" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="J1550" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="J1551" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="J1552" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="J1553" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="J1554" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="J1555" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="J1556" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="J1557" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="J1558" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="J1559" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="J1560" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="J1561" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="J1562" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="J1563" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="J1564" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="J1565" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="J1566" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="J1567" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="J1568" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="J1569" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="J1570" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="J1571" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="J1572" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="J1573" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="J1574" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="J1575" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="J1576" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="J1577" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="J1578" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="J1579" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="J1580" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="J1581" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="J1582" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="J1583" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="J1584" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="J1585" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="J1586" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="J1587" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="J1588" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="J1589" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="J1590" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="J1591" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="J1592" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="J1593" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="J1594" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="J1595" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="J1596" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="J1597" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="J1598" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="J1599" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="J1600" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="J1601" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="J1602" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="J1603" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="J1604" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="J1605" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="J1606" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="J1607" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="J1608" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="J1609" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="J1610" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="J1611" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="J1612" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="J1613" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="J1614" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="J1615" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="J1616" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="J1617" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="J1618" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="J1619" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="J1620" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="J1621" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="J1622" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="J1623" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="J1624" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="J1625" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="J1626" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="J1627" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="J1628" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="J1629" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="J1630" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="J1631" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="J1632" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="J1633" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="J1634" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="J1635" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="J1636" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="J1637" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="J1638" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="J1639" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="J1640" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="J1641" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="J1642" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="J1643" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="J1644" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="J1645" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="J1646" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="J1647" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="J1648" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="J1649" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="J1650" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="J1651" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="J1652" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="J1653" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="J1654" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="J1655" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="J1656" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="J1657" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="J1658" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="J1659" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="J1660" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="J1661" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="J1662" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="J1663" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="J1664" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="J1665" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="J1666" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="J1667" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="J1668" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="J1669" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="J1670" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="J1671" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="J1672" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="J1673" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="J1674" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="J1675" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="J1676" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="J1677" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="J1678" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="J1679" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="J1680" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="J1681" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="J1682" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="J1683" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="J1684" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="J1685" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="J1686" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="J1687" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="J1688" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="J1689" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="J1690" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="J1691" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="J1692" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="J1693" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="J1694" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="J1695" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="J1696" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="J1697" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="J1698" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="J1699" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="J1700" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="J1701" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="J1702" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="J1703" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="J1704" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="J1705" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="J1706" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="J1707" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="J1708" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="J1709" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="J1710" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="J1711" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="J1712" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="J1713" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="J1714" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="J1715" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="J1716" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="J1717" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="J1718" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="J1719" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="J1720" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="J1721" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="J1722" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="J1723" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="J1724" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="J1725" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="J1726" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="J1727" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="J1728" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="J1729" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="J1730" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="J1731" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="J1732" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="J1733" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="J1734" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="J1735" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="J1736" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="J1737" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="J1738" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="J1739" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="J1740" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="J1741" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="J1742" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="J1743" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="J1744" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="J1745" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="J1746" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="J1747" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="J1748" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="J1749" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="J1750" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="J1751" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="J1752" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="J1753" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="J1754" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="J1755" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="J1756" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="J1757" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="J1758" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="J1759" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="J1760" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="J1761" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="J1762" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="J1763" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="J1764" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="J1765" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="J1766" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="J1767" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="J1768" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="J1769" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="J1770" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="J1771" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="J1772" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1773">
+      <c r="J1773" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="J1774" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="J1775" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="J1776" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="J1777" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="J1778" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="J1779" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="J1780" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="J1781" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="J1782" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="J1783" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1784">
+      <c r="J1784" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1785">
+      <c r="J1785" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1786">
+      <c r="J1786" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1787">
+      <c r="J1787" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="J1788" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1789">
+      <c r="J1789" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1790">
+      <c r="J1790" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1791">
+      <c r="J1791" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1792">
+      <c r="J1792" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1793">
+      <c r="J1793" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1794">
+      <c r="J1794" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1795">
+      <c r="J1795" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1796">
+      <c r="J1796" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1797">
+      <c r="J1797" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1798">
+      <c r="J1798" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1799">
+      <c r="J1799" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1800">
+      <c r="J1800" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1801">
+      <c r="J1801" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1802">
+      <c r="J1802" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1803">
+      <c r="J1803" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1804">
+      <c r="J1804" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1805">
+      <c r="J1805" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1806">
+      <c r="J1806" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1807">
+      <c r="J1807" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1808">
+      <c r="J1808" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1809">
+      <c r="J1809" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1810">
+      <c r="J1810" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1811">
+      <c r="J1811" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1812">
+      <c r="J1812" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1813">
+      <c r="J1813" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1814">
+      <c r="J1814" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1815">
+      <c r="J1815" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1816">
+      <c r="J1816" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1817">
+      <c r="J1817" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1818">
+      <c r="J1818" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1819">
+      <c r="J1819" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1820">
+      <c r="J1820" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1821">
+      <c r="J1821" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1822">
+      <c r="J1822" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1823">
+      <c r="J1823" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1824">
+      <c r="J1824" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1825">
+      <c r="J1825" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1826">
+      <c r="J1826" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1827">
+      <c r="J1827" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1828">
+      <c r="J1828" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="J1829" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1830">
+      <c r="J1830" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1831">
+      <c r="J1831" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="J1832" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="J1833" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1834">
+      <c r="J1834" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="J1835" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="J1836" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="J1837" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="J1838" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="J1839" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="J1840" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="J1841" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="J1842" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="J1843" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="J1844" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="J1845" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="J1846" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="J1847" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="J1848" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="J1849" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="J1850" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="J1851" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="J1852" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="J1853" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="J1854" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="J1855" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="J1856" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1857">
+      <c r="J1857" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1858">
+      <c r="J1858" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1859">
+      <c r="J1859" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1860">
+      <c r="J1860" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1861">
+      <c r="J1861" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1862">
+      <c r="J1862" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1863">
+      <c r="J1863" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1864">
+      <c r="J1864" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1865">
+      <c r="J1865" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1866">
+      <c r="J1866" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="J1867" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1868">
+      <c r="J1868" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1869">
+      <c r="J1869" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1870">
+      <c r="J1870" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1871">
+      <c r="J1871" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1872">
+      <c r="J1872" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="J1873" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="J1874" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="J1875" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1876">
+      <c r="J1876" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1877">
+      <c r="J1877" t="inlineStr">
+        <is>
+          <t>tavarkere</t>
+        </is>
+      </c>
+    </row>
+    <row r="1878">
+      <c r="J1878" t="inlineStr">
+        <is>
+          <t>jpnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="J1879" t="inlineStr">
         <is>
           <t>jpnagar</t>
         </is>
@@ -22634,10 +27786,6 @@
           <t>Box came out of safe</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>3</t>
@@ -22648,9 +27796,6 @@
           <t>S14, S2, S3</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>tavakere</t>
@@ -22663,17 +27808,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr">
         <is>
           <t>Box opened outside of table</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>6</t>
@@ -22686,17 +27825,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>Box opened(in frames)</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>18</t>
@@ -22709,17 +27842,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Box closed(in frames)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>8</t>
@@ -22747,10 +27874,6 @@
           <t>Box closed(in frames)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>2</t>
@@ -22761,9 +27884,6 @@
           <t>S2</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>tavakere</t>
@@ -22791,10 +27911,6 @@
           <t>Box came out of safe</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>1</t>
@@ -22805,9 +27921,6 @@
           <t>S3</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>tavakere</t>
@@ -22820,17 +27933,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
           <t>Box opened(in frames)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>6</t>
@@ -22843,17 +27950,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>Box closed(in frames)</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
           <t>2</t>
@@ -22881,10 +27982,6 @@
           <t>Box opened(in frames)</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
           <t>16</t>
@@ -22895,9 +27992,6 @@
           <t>S3</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>tavakere</t>
@@ -22910,17 +28004,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
           <t>Box closed(in frames)</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>3</t>
@@ -22948,10 +28036,6 @@
           <t>Box came out of safe</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
           <t>1</t>
@@ -22962,9 +28046,6 @@
           <t>S4</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>tavakere</t>
@@ -22977,17 +28058,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
           <t>Box opened(in frames)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
           <t>28</t>
@@ -23000,17 +28075,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>Box closed(in frames)</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>4</t>
@@ -23038,10 +28107,6 @@
           <t>Box came out of safe</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>1</t>
@@ -23052,9 +28117,6 @@
           <t>S5</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>tavakere</t>
@@ -23067,17 +28129,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
           <t>Box opened(in frames)</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
           <t>92</t>
@@ -23090,17 +28146,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
           <t>Box closed(in frames)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
           <t>4</t>
@@ -23128,10 +28178,6 @@
           <t>Box opened(in frames)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
           <t>13</t>
@@ -23142,9 +28188,6 @@
           <t>S5</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>tavakere</t>
@@ -23157,17 +28200,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>Box closed(in frames)</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>1</t>
